--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_C_AVSWAR-CSTD-A0-03-A-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_C_AVSWAR-CSTD-A0-03-A-C0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\10_mcu\19epfv3_mcu_app_mainline\src\IpcApplication\Vom\Alert\matrix\scc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_JPlaptop\BEV_MCU\git_v043_AlertFix\src\PE1VM1\App\MET\IpcApplication\Vom\Alert\matrix\scc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F83A23FA-412C-4CF6-B230-4D7AF7A7F81D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA66049-F0D0-4167-A311-C506B7E6DF0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-7575" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14265" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙（承認）" sheetId="16" r:id="rId1"/>
@@ -603,7 +603,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2447" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2452" uniqueCount="287">
   <si>
     <t>更新履歴</t>
     <phoneticPr fontId="2"/>
@@ -2724,9 +2724,6 @@
     <t>C_AVSWAR-CSTD-A0-MEF01-REQ03-</t>
   </si>
   <si>
-    <t>AVSW</t>
-  </si>
-  <si>
     <t>OPT</t>
   </si>
   <si>
@@ -2739,9 +2736,6 @@
 AND ┬ IGR(IG2) = ON
 　　└ AVSEXT = 001b以外を4.2s間で2回以上連続受信</t>
     <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>○</t>
   </si>
   <si>
     <t>AVSMINF</t>
@@ -2956,9 +2950,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>(株)NTTデータMSE</t>
-  </si>
-  <si>
     <t>デンソーテクノ(株)</t>
   </si>
   <si>
@@ -2983,6 +2974,35 @@
   </si>
   <si>
     <t>https://aip01.dndev.net/svn/met/toyota/std/rd/spec/19PFver3/tags/00.Product/v6.4.d/</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1.0.2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>DTPH Kiko</t>
+  </si>
+  <si>
+    <t>－</t>
+  </si>
+  <si>
+    <t>(株)デンソー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>BEVシス検ADAS
+課題対応（BEV3CDCMET-2941）
+[Matrix]シート
+・RWの記載を変更（○→ー）
+[CH_Design]シート
+・RWの記載を変更（AVSW→ー）</t>
+    <rPh sb="11" eb="13">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>タイオウ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3323,7 +3343,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="88">
+  <borders count="90">
     <border>
       <left/>
       <right/>
@@ -4462,6 +4482,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -4474,7 +4520,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="317">
+  <cellXfs count="322">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5219,6 +5265,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="27" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5414,6 +5472,9 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -5515,16 +5576,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>57079</xdr:colOff>
+      <xdr:colOff>103957</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>57079</xdr:rowOff>
+      <xdr:rowOff>63989</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0E458AE-570E-439F-90AF-BFDC7D8DE750}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9B32820-2B31-0C11-3BB1-F50D7073140B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5540,7 +5601,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6000750" y="7924800"/>
+          <a:off x="5490882" y="7776882"/>
           <a:ext cx="571429" cy="571429"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -8477,8 +8538,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="40173088" y="6633882"/>
-          <a:ext cx="15413601" cy="9777419"/>
+          <a:off x="36309300" y="6448425"/>
+          <a:ext cx="13783332" cy="9418270"/>
           <a:chOff x="40173088" y="6633882"/>
           <a:chExt cx="15413601" cy="9777419"/>
         </a:xfrm>
@@ -9979,9 +10040,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B67217F-73C6-4474-923D-65746D362F67}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:AN49"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="40" width="2.25" style="203" customWidth="1"/>
+    <col min="1" max="40" width="2.26953125" style="203" customWidth="1"/>
     <col min="41" max="16384" width="9" style="203"/>
   </cols>
   <sheetData>
@@ -10322,91 +10383,91 @@
       <c r="AN8" s="206"/>
     </row>
     <row r="9" spans="1:40" ht="28.5" customHeight="1">
-      <c r="A9" s="253" t="str">
+      <c r="A9" s="257" t="str">
         <f ca="1">MID(CELL("filename",A1), FIND("[",CELL("filename",A1))+1, FIND("]",CELL("filename",A1))-FIND("[",CELL("filename",A1))-6)</f>
         <v>alert_C_AVSWAR-CSTD-A0-03-A-C0</v>
       </c>
-      <c r="B9" s="254"/>
-      <c r="C9" s="254"/>
-      <c r="D9" s="254"/>
-      <c r="E9" s="254"/>
-      <c r="F9" s="254"/>
-      <c r="G9" s="254"/>
-      <c r="H9" s="254"/>
-      <c r="I9" s="254"/>
-      <c r="J9" s="254"/>
-      <c r="K9" s="254"/>
-      <c r="L9" s="254"/>
-      <c r="M9" s="254"/>
-      <c r="N9" s="254"/>
-      <c r="O9" s="254"/>
-      <c r="P9" s="254"/>
-      <c r="Q9" s="254"/>
-      <c r="R9" s="254"/>
-      <c r="S9" s="254"/>
-      <c r="T9" s="254"/>
-      <c r="U9" s="254"/>
-      <c r="V9" s="254"/>
-      <c r="W9" s="254"/>
-      <c r="X9" s="254"/>
-      <c r="Y9" s="254"/>
-      <c r="Z9" s="254"/>
-      <c r="AA9" s="254"/>
-      <c r="AB9" s="254"/>
-      <c r="AC9" s="254"/>
-      <c r="AD9" s="254"/>
-      <c r="AE9" s="254"/>
-      <c r="AF9" s="254"/>
-      <c r="AG9" s="254"/>
-      <c r="AH9" s="254"/>
-      <c r="AI9" s="254"/>
-      <c r="AJ9" s="254"/>
-      <c r="AK9" s="254"/>
-      <c r="AL9" s="254"/>
-      <c r="AM9" s="254"/>
-      <c r="AN9" s="255"/>
+      <c r="B9" s="258"/>
+      <c r="C9" s="258"/>
+      <c r="D9" s="258"/>
+      <c r="E9" s="258"/>
+      <c r="F9" s="258"/>
+      <c r="G9" s="258"/>
+      <c r="H9" s="258"/>
+      <c r="I9" s="258"/>
+      <c r="J9" s="258"/>
+      <c r="K9" s="258"/>
+      <c r="L9" s="258"/>
+      <c r="M9" s="258"/>
+      <c r="N9" s="258"/>
+      <c r="O9" s="258"/>
+      <c r="P9" s="258"/>
+      <c r="Q9" s="258"/>
+      <c r="R9" s="258"/>
+      <c r="S9" s="258"/>
+      <c r="T9" s="258"/>
+      <c r="U9" s="258"/>
+      <c r="V9" s="258"/>
+      <c r="W9" s="258"/>
+      <c r="X9" s="258"/>
+      <c r="Y9" s="258"/>
+      <c r="Z9" s="258"/>
+      <c r="AA9" s="258"/>
+      <c r="AB9" s="258"/>
+      <c r="AC9" s="258"/>
+      <c r="AD9" s="258"/>
+      <c r="AE9" s="258"/>
+      <c r="AF9" s="258"/>
+      <c r="AG9" s="258"/>
+      <c r="AH9" s="258"/>
+      <c r="AI9" s="258"/>
+      <c r="AJ9" s="258"/>
+      <c r="AK9" s="258"/>
+      <c r="AL9" s="258"/>
+      <c r="AM9" s="258"/>
+      <c r="AN9" s="259"/>
     </row>
     <row r="10" spans="1:40" ht="28.5" customHeight="1">
-      <c r="A10" s="253"/>
-      <c r="B10" s="254"/>
-      <c r="C10" s="254"/>
-      <c r="D10" s="254"/>
-      <c r="E10" s="254"/>
-      <c r="F10" s="254"/>
-      <c r="G10" s="254"/>
-      <c r="H10" s="254"/>
-      <c r="I10" s="254"/>
-      <c r="J10" s="254"/>
-      <c r="K10" s="254"/>
-      <c r="L10" s="254"/>
-      <c r="M10" s="254"/>
-      <c r="N10" s="254"/>
-      <c r="O10" s="254"/>
-      <c r="P10" s="254"/>
-      <c r="Q10" s="254"/>
-      <c r="R10" s="254"/>
-      <c r="S10" s="254"/>
-      <c r="T10" s="254"/>
-      <c r="U10" s="254"/>
-      <c r="V10" s="254"/>
-      <c r="W10" s="254"/>
-      <c r="X10" s="254"/>
-      <c r="Y10" s="254"/>
-      <c r="Z10" s="254"/>
-      <c r="AA10" s="254"/>
-      <c r="AB10" s="254"/>
-      <c r="AC10" s="254"/>
-      <c r="AD10" s="254"/>
-      <c r="AE10" s="254"/>
-      <c r="AF10" s="254"/>
-      <c r="AG10" s="254"/>
-      <c r="AH10" s="254"/>
-      <c r="AI10" s="254"/>
-      <c r="AJ10" s="254"/>
-      <c r="AK10" s="254"/>
-      <c r="AL10" s="254"/>
-      <c r="AM10" s="254"/>
-      <c r="AN10" s="255"/>
+      <c r="A10" s="257"/>
+      <c r="B10" s="258"/>
+      <c r="C10" s="258"/>
+      <c r="D10" s="258"/>
+      <c r="E10" s="258"/>
+      <c r="F10" s="258"/>
+      <c r="G10" s="258"/>
+      <c r="H10" s="258"/>
+      <c r="I10" s="258"/>
+      <c r="J10" s="258"/>
+      <c r="K10" s="258"/>
+      <c r="L10" s="258"/>
+      <c r="M10" s="258"/>
+      <c r="N10" s="258"/>
+      <c r="O10" s="258"/>
+      <c r="P10" s="258"/>
+      <c r="Q10" s="258"/>
+      <c r="R10" s="258"/>
+      <c r="S10" s="258"/>
+      <c r="T10" s="258"/>
+      <c r="U10" s="258"/>
+      <c r="V10" s="258"/>
+      <c r="W10" s="258"/>
+      <c r="X10" s="258"/>
+      <c r="Y10" s="258"/>
+      <c r="Z10" s="258"/>
+      <c r="AA10" s="258"/>
+      <c r="AB10" s="258"/>
+      <c r="AC10" s="258"/>
+      <c r="AD10" s="258"/>
+      <c r="AE10" s="258"/>
+      <c r="AF10" s="258"/>
+      <c r="AG10" s="258"/>
+      <c r="AH10" s="258"/>
+      <c r="AI10" s="258"/>
+      <c r="AJ10" s="258"/>
+      <c r="AK10" s="258"/>
+      <c r="AL10" s="258"/>
+      <c r="AM10" s="258"/>
+      <c r="AN10" s="259"/>
     </row>
     <row r="11" spans="1:40" ht="13.5" customHeight="1">
       <c r="A11" s="204"/>
@@ -11063,8 +11124,8 @@
       <c r="V26" s="205"/>
       <c r="W26" s="205"/>
       <c r="X26" s="205"/>
-      <c r="Y26" s="207" t="s">
-        <v>278</v>
+      <c r="Y26" s="143" t="s">
+        <v>285</v>
       </c>
       <c r="Z26" s="205"/>
       <c r="AA26" s="205"/>
@@ -11107,27 +11168,27 @@
       <c r="V27" s="205"/>
       <c r="W27" s="205"/>
       <c r="X27" s="205"/>
-      <c r="Y27" s="250" t="s">
+      <c r="Y27" s="254" t="s">
         <v>216</v>
       </c>
-      <c r="Z27" s="251"/>
-      <c r="AA27" s="251"/>
-      <c r="AB27" s="251"/>
-      <c r="AC27" s="252"/>
-      <c r="AD27" s="250" t="s">
+      <c r="Z27" s="255"/>
+      <c r="AA27" s="255"/>
+      <c r="AB27" s="255"/>
+      <c r="AC27" s="256"/>
+      <c r="AD27" s="254" t="s">
         <v>217</v>
       </c>
-      <c r="AE27" s="251"/>
-      <c r="AF27" s="251"/>
-      <c r="AG27" s="251"/>
-      <c r="AH27" s="252"/>
-      <c r="AI27" s="256" t="s">
+      <c r="AE27" s="255"/>
+      <c r="AF27" s="255"/>
+      <c r="AG27" s="255"/>
+      <c r="AH27" s="256"/>
+      <c r="AI27" s="260" t="s">
         <v>218</v>
       </c>
-      <c r="AJ27" s="251"/>
-      <c r="AK27" s="251"/>
-      <c r="AL27" s="251"/>
-      <c r="AM27" s="252"/>
+      <c r="AJ27" s="255"/>
+      <c r="AK27" s="255"/>
+      <c r="AL27" s="255"/>
+      <c r="AM27" s="256"/>
       <c r="AN27" s="206"/>
     </row>
     <row r="28" spans="1:40" ht="13.5" customHeight="1">
@@ -11412,7 +11473,7 @@
       <c r="W34" s="205"/>
       <c r="X34" s="205"/>
       <c r="Y34" s="207" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="Z34" s="205"/>
       <c r="AA34" s="205"/>
@@ -11455,27 +11516,27 @@
       <c r="V35" s="205"/>
       <c r="W35" s="205"/>
       <c r="X35" s="205"/>
-      <c r="Y35" s="250" t="s">
+      <c r="Y35" s="254" t="s">
         <v>216</v>
       </c>
-      <c r="Z35" s="251"/>
-      <c r="AA35" s="251"/>
-      <c r="AB35" s="251"/>
-      <c r="AC35" s="252"/>
-      <c r="AD35" s="250" t="s">
+      <c r="Z35" s="255"/>
+      <c r="AA35" s="255"/>
+      <c r="AB35" s="255"/>
+      <c r="AC35" s="256"/>
+      <c r="AD35" s="254" t="s">
         <v>217</v>
       </c>
-      <c r="AE35" s="251"/>
-      <c r="AF35" s="251"/>
-      <c r="AG35" s="251"/>
-      <c r="AH35" s="252"/>
-      <c r="AI35" s="256" t="s">
+      <c r="AE35" s="255"/>
+      <c r="AF35" s="255"/>
+      <c r="AG35" s="255"/>
+      <c r="AH35" s="256"/>
+      <c r="AI35" s="260" t="s">
         <v>218</v>
       </c>
-      <c r="AJ35" s="251"/>
-      <c r="AK35" s="251"/>
-      <c r="AL35" s="251"/>
-      <c r="AM35" s="252"/>
+      <c r="AJ35" s="255"/>
+      <c r="AK35" s="255"/>
+      <c r="AL35" s="255"/>
+      <c r="AM35" s="256"/>
       <c r="AN35" s="206"/>
     </row>
     <row r="36" spans="1:40" ht="13.5" customHeight="1">
@@ -11805,27 +11866,27 @@
       <c r="V43" s="205"/>
       <c r="W43" s="205"/>
       <c r="X43" s="205"/>
-      <c r="Y43" s="250" t="s">
+      <c r="Y43" s="254" t="s">
         <v>216</v>
       </c>
-      <c r="Z43" s="251"/>
-      <c r="AA43" s="251"/>
-      <c r="AB43" s="251"/>
-      <c r="AC43" s="252"/>
-      <c r="AD43" s="250" t="s">
+      <c r="Z43" s="255"/>
+      <c r="AA43" s="255"/>
+      <c r="AB43" s="255"/>
+      <c r="AC43" s="256"/>
+      <c r="AD43" s="254" t="s">
         <v>217</v>
       </c>
-      <c r="AE43" s="251"/>
-      <c r="AF43" s="251"/>
-      <c r="AG43" s="251"/>
-      <c r="AH43" s="252"/>
-      <c r="AI43" s="250" t="s">
+      <c r="AE43" s="255"/>
+      <c r="AF43" s="255"/>
+      <c r="AG43" s="255"/>
+      <c r="AH43" s="256"/>
+      <c r="AI43" s="254" t="s">
         <v>218</v>
       </c>
-      <c r="AJ43" s="251"/>
-      <c r="AK43" s="251"/>
-      <c r="AL43" s="251"/>
-      <c r="AM43" s="252"/>
+      <c r="AJ43" s="255"/>
+      <c r="AK43" s="255"/>
+      <c r="AL43" s="255"/>
+      <c r="AM43" s="256"/>
       <c r="AN43" s="206"/>
     </row>
     <row r="44" spans="1:40" ht="13.5" customHeight="1">
@@ -12108,14 +12169,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:X13"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="4.5" customWidth="1"/>
+    <col min="1" max="1" width="4.453125" customWidth="1"/>
     <col min="2" max="2" width="9" style="9" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="69.5" customWidth="1"/>
-    <col min="5" max="6" width="12.75" customWidth="1"/>
-    <col min="7" max="22" width="13.125" hidden="1" customWidth="1"/>
-    <col min="23" max="24" width="13.125" customWidth="1"/>
+    <col min="4" max="4" width="69.453125" customWidth="1"/>
+    <col min="5" max="6" width="12.7265625" customWidth="1"/>
+    <col min="7" max="22" width="13.08984375" hidden="1" customWidth="1"/>
+    <col min="23" max="24" width="13.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:24" ht="25.5" customHeight="1">
@@ -12126,18 +12187,18 @@
       <c r="H2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="257" t="s">
+      <c r="I2" s="261" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="257"/>
-      <c r="K2" s="257"/>
-      <c r="L2" s="257"/>
-      <c r="M2" s="257"/>
-      <c r="N2" s="257"/>
-      <c r="O2" s="257"/>
-      <c r="P2" s="257"/>
-      <c r="Q2" s="257"/>
-      <c r="R2" s="257"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
+      <c r="M2" s="261"/>
+      <c r="N2" s="261"/>
+      <c r="O2" s="261"/>
+      <c r="P2" s="261"/>
+      <c r="Q2" s="261"/>
+      <c r="R2" s="261"/>
     </row>
     <row r="3" spans="2:24" ht="25.5" customHeight="1">
       <c r="C3" s="6"/>
@@ -12150,25 +12211,25 @@
       <c r="H3" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="I3" s="258" t="s">
+      <c r="I3" s="262" t="s">
         <v>175</v>
       </c>
-      <c r="J3" s="259"/>
-      <c r="K3" s="259"/>
-      <c r="L3" s="259"/>
-      <c r="M3" s="259"/>
-      <c r="N3" s="259"/>
-      <c r="O3" s="259"/>
-      <c r="P3" s="259"/>
-      <c r="Q3" s="259"/>
-      <c r="R3" s="259"/>
+      <c r="J3" s="263"/>
+      <c r="K3" s="263"/>
+      <c r="L3" s="263"/>
+      <c r="M3" s="263"/>
+      <c r="N3" s="263"/>
+      <c r="O3" s="263"/>
+      <c r="P3" s="263"/>
+      <c r="Q3" s="263"/>
+      <c r="R3" s="263"/>
     </row>
     <row r="4" spans="2:24" ht="25.5" customHeight="1">
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="22" t="str">
         <f>DGET(B8:C14,"Ver.",H4:H5)</f>
-        <v>1.0.1</v>
+        <v>1.0.2</v>
       </c>
       <c r="F4" s="6"/>
       <c r="H4" s="9" t="s">
@@ -12182,45 +12243,45 @@
       <c r="F5" s="6"/>
       <c r="H5" s="11">
         <f>MAX(B9:B14)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:24" ht="13.5" thickBot="1"/>
+    <row r="7" spans="2:24">
+      <c r="C7" s="266" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="267"/>
+      <c r="E7" s="268" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="2:24" ht="14.25" thickBot="1"/>
-    <row r="7" spans="2:24">
-      <c r="C7" s="262" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="263"/>
-      <c r="E7" s="264" t="s">
-        <v>2</v>
-      </c>
-      <c r="F7" s="264"/>
-      <c r="G7" s="265" t="s">
+      <c r="F7" s="268"/>
+      <c r="G7" s="269" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="265"/>
-      <c r="I7" s="265"/>
-      <c r="J7" s="265"/>
-      <c r="K7" s="265"/>
-      <c r="L7" s="265"/>
-      <c r="M7" s="266" t="s">
+      <c r="H7" s="269"/>
+      <c r="I7" s="269"/>
+      <c r="J7" s="269"/>
+      <c r="K7" s="269"/>
+      <c r="L7" s="269"/>
+      <c r="M7" s="270" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="266"/>
-      <c r="O7" s="266"/>
-      <c r="P7" s="266"/>
-      <c r="Q7" s="266"/>
-      <c r="R7" s="267"/>
-      <c r="S7" s="260" t="s">
+      <c r="N7" s="270"/>
+      <c r="O7" s="270"/>
+      <c r="P7" s="270"/>
+      <c r="Q7" s="270"/>
+      <c r="R7" s="271"/>
+      <c r="S7" s="264" t="s">
         <v>224</v>
       </c>
-      <c r="T7" s="260"/>
-      <c r="U7" s="260"/>
-      <c r="V7" s="260"/>
-      <c r="W7" s="260"/>
-      <c r="X7" s="261"/>
-    </row>
-    <row r="8" spans="2:24" ht="27.75" thickBot="1">
+      <c r="T7" s="264"/>
+      <c r="U7" s="264"/>
+      <c r="V7" s="264"/>
+      <c r="W7" s="264"/>
+      <c r="X7" s="265"/>
+    </row>
+    <row r="8" spans="2:24" ht="26.5" thickBot="1">
       <c r="B8" s="9" t="s">
         <v>91</v>
       </c>
@@ -12291,7 +12352,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:24" ht="14.25" thickTop="1">
+    <row r="9" spans="2:24" ht="13.5" thickTop="1">
       <c r="B9" s="9">
         <f>IF(C9=0,0,ROW()-ROW($B$8))</f>
         <v>1</v>
@@ -12363,16 +12424,16 @@
         <v>45275</v>
       </c>
     </row>
-    <row r="10" spans="2:24" ht="67.5">
+    <row r="10" spans="2:24" ht="65">
       <c r="B10" s="9">
         <f>IF(C10=0,0,ROW()-ROW($B$8))</f>
         <v>2</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D10" s="187" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>30</v>
@@ -12409,21 +12470,29 @@
       <c r="U10" s="1"/>
       <c r="V10" s="192"/>
       <c r="W10" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="X10" s="188">
         <v>45807</v>
       </c>
     </row>
-    <row r="11" spans="2:24">
+    <row r="11" spans="2:24" ht="91">
       <c r="B11" s="9">
         <f>IF(C11=0,0,ROW()-ROW($B$8))</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="187"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="C11" s="250" t="s">
+        <v>282</v>
+      </c>
+      <c r="D11" s="251" t="s">
+        <v>286</v>
+      </c>
+      <c r="E11" s="252" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="252" t="s">
+        <v>30</v>
+      </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -12440,8 +12509,12 @@
       <c r="T11" s="13"/>
       <c r="U11" s="13"/>
       <c r="V11" s="13"/>
-      <c r="W11" s="13"/>
-      <c r="X11" s="188"/>
+      <c r="W11" s="321" t="s">
+        <v>283</v>
+      </c>
+      <c r="X11" s="253">
+        <v>46008</v>
+      </c>
     </row>
     <row r="12" spans="2:24">
       <c r="B12" s="9">
@@ -12471,7 +12544,7 @@
       <c r="W12" s="13"/>
       <c r="X12" s="188"/>
     </row>
-    <row r="13" spans="2:24" ht="14.25" thickBot="1">
+    <row r="13" spans="2:24" ht="13.5" thickBot="1">
       <c r="B13" s="9">
         <f>IF(C13=0,0,ROW()-ROW($B$8))</f>
         <v>0</v>
@@ -12525,11 +12598,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:E39"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="4.625" customWidth="1"/>
-    <col min="3" max="3" width="3.5" customWidth="1"/>
-    <col min="4" max="4" width="17.5" customWidth="1"/>
+    <col min="2" max="2" width="4.6328125" customWidth="1"/>
+    <col min="3" max="3" width="3.453125" customWidth="1"/>
+    <col min="4" max="4" width="17.453125" customWidth="1"/>
     <col min="5" max="5" width="106" customWidth="1"/>
   </cols>
   <sheetData>
@@ -12543,13 +12616,13 @@
         <v>135</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="14.25" thickBot="1">
+    <row r="6" spans="2:5" ht="13.5" thickBot="1">
       <c r="B6" s="143" t="s">
         <v>126</v>
       </c>
       <c r="C6" s="143"/>
     </row>
-    <row r="7" spans="2:5" ht="14.25" thickBot="1">
+    <row r="7" spans="2:5" ht="13.5" thickBot="1">
       <c r="C7" s="73" t="s">
         <v>128</v>
       </c>
@@ -12574,7 +12647,7 @@
       <c r="D9" s="155"/>
       <c r="E9" s="154"/>
     </row>
-    <row r="10" spans="2:5" ht="14.25" thickBot="1">
+    <row r="10" spans="2:5" ht="13.5" thickBot="1">
       <c r="C10" s="151"/>
       <c r="D10" s="84"/>
       <c r="E10" s="5"/>
@@ -12582,14 +12655,14 @@
     <row r="11" spans="2:5">
       <c r="C11" s="149"/>
     </row>
-    <row r="12" spans="2:5" ht="14.25" thickBot="1">
+    <row r="12" spans="2:5" ht="13.5" thickBot="1">
       <c r="B12" s="144" t="s">
         <v>127</v>
       </c>
       <c r="C12" s="80"/>
       <c r="D12" s="80"/>
     </row>
-    <row r="13" spans="2:5" ht="14.25" thickBot="1">
+    <row r="13" spans="2:5" ht="13.5" thickBot="1">
       <c r="B13" s="145"/>
       <c r="C13" s="150" t="s">
         <v>128</v>
@@ -12601,7 +12674,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="14.25" thickTop="1">
+    <row r="14" spans="2:5" ht="13.5" thickTop="1">
       <c r="C14" s="147">
         <v>0</v>
       </c>
@@ -12678,17 +12751,17 @@
         <v>169</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="14.25" thickBot="1">
+    <row r="21" spans="2:5" ht="13.5" thickBot="1">
       <c r="C21" s="151"/>
       <c r="D21" s="84"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="24" spans="2:5" ht="14.25" thickBot="1">
+    <row r="24" spans="2:5" ht="13.5" thickBot="1">
       <c r="B24" s="143" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="14.25" thickBot="1">
+    <row r="25" spans="2:5" ht="13.5" thickBot="1">
       <c r="C25" s="150" t="s">
         <v>128</v>
       </c>
@@ -12775,26 +12848,26 @@
       <c r="D33" s="83"/>
       <c r="E33" s="69"/>
     </row>
-    <row r="34" spans="2:5" ht="14.25" thickBot="1">
+    <row r="34" spans="2:5" ht="13.5" thickBot="1">
       <c r="C34" s="151"/>
       <c r="D34" s="84"/>
       <c r="E34" s="5"/>
     </row>
-    <row r="37" spans="2:5" ht="14.25" thickBot="1">
+    <row r="37" spans="2:5" ht="13.5" thickBot="1">
       <c r="B37" s="143" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="38" spans="2:5">
-      <c r="C38" s="268"/>
-      <c r="D38" s="269"/>
+      <c r="C38" s="272"/>
+      <c r="D38" s="273"/>
       <c r="E38" s="108" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="14.25" thickBot="1">
-      <c r="C39" s="270"/>
-      <c r="D39" s="271"/>
+    <row r="39" spans="2:5" ht="13.5" thickBot="1">
+      <c r="C39" s="274"/>
+      <c r="D39" s="275"/>
       <c r="E39" s="5" t="s">
         <v>118</v>
       </c>
@@ -12822,133 +12895,133 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:N37"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="26.75" customWidth="1"/>
-    <col min="9" max="9" width="20.875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="26.7265625" customWidth="1"/>
+    <col min="9" max="9" width="20.90625" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="14.25" thickBot="1"/>
+    <row r="1" spans="2:14" ht="13.5" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="284" t="s">
+      <c r="B2" s="288" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="285"/>
-      <c r="D2" s="272" t="s">
-        <v>283</v>
-      </c>
-      <c r="E2" s="273"/>
-      <c r="F2" s="273"/>
-      <c r="G2" s="273"/>
-      <c r="H2" s="274"/>
+      <c r="C2" s="289"/>
+      <c r="D2" s="276" t="s">
+        <v>280</v>
+      </c>
+      <c r="E2" s="277"/>
+      <c r="F2" s="277"/>
+      <c r="G2" s="277"/>
+      <c r="H2" s="278"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="286" t="s">
+      <c r="B3" s="290" t="s">
         <v>115</v>
       </c>
-      <c r="C3" s="287"/>
-      <c r="D3" s="290" t="s">
-        <v>284</v>
-      </c>
-      <c r="E3" s="291"/>
-      <c r="F3" s="291"/>
-      <c r="G3" s="291"/>
-      <c r="H3" s="292"/>
-    </row>
-    <row r="4" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B4" s="288" t="s">
+      <c r="C3" s="291"/>
+      <c r="D3" s="294" t="s">
+        <v>281</v>
+      </c>
+      <c r="E3" s="295"/>
+      <c r="F3" s="295"/>
+      <c r="G3" s="295"/>
+      <c r="H3" s="296"/>
+    </row>
+    <row r="4" spans="2:14" ht="13.5" thickBot="1">
+      <c r="B4" s="292" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="289"/>
-      <c r="D4" s="275" t="str">
+      <c r="C4" s="293"/>
+      <c r="D4" s="279" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_C_AVSWAR-CSTD-A0-03-A-C0.c</v>
       </c>
-      <c r="E4" s="276"/>
-      <c r="F4" s="276"/>
-      <c r="G4" s="276"/>
-      <c r="H4" s="277"/>
-    </row>
-    <row r="5" spans="2:14" ht="14.25" thickBot="1">
+      <c r="E4" s="280"/>
+      <c r="F4" s="280"/>
+      <c r="G4" s="280"/>
+      <c r="H4" s="281"/>
+    </row>
+    <row r="5" spans="2:14" ht="13.5" thickBot="1">
       <c r="D5" t="str">
         <f ca="1">IF(LEN(表紙!D3&amp;".c") = LENB(表紙!D3&amp;".c"),"※モジュール名 全角チェックOK","※モジュール名 全角チェックNG：ファイル名に全角文字が使用されています！")</f>
         <v>※モジュール名 全角チェックOK</v>
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="284" t="s">
+      <c r="B6" s="288" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="285"/>
-      <c r="D6" s="278" t="str">
+      <c r="C6" s="289"/>
+      <c r="D6" s="282" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>C_AVSWAR</v>
       </c>
-      <c r="E6" s="279"/>
-      <c r="F6" s="279"/>
-      <c r="G6" s="279"/>
-      <c r="H6" s="280"/>
+      <c r="E6" s="283"/>
+      <c r="F6" s="283"/>
+      <c r="G6" s="283"/>
+      <c r="H6" s="284"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="286" t="s">
+      <c r="B7" s="290" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="287"/>
-      <c r="D7" s="281">
+      <c r="C7" s="291"/>
+      <c r="D7" s="285">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="282"/>
-      <c r="F7" s="282"/>
-      <c r="G7" s="282"/>
-      <c r="H7" s="283"/>
+      <c r="E7" s="286"/>
+      <c r="F7" s="286"/>
+      <c r="G7" s="286"/>
+      <c r="H7" s="287"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="286" t="s">
+      <c r="B8" s="290" t="s">
         <v>94</v>
       </c>
-      <c r="C8" s="287"/>
-      <c r="D8" s="281" t="str">
+      <c r="C8" s="291"/>
+      <c r="D8" s="285" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_C_AVSWAR_MTRX</v>
       </c>
-      <c r="E8" s="282"/>
-      <c r="F8" s="282"/>
-      <c r="G8" s="282"/>
-      <c r="H8" s="283"/>
+      <c r="E8" s="286"/>
+      <c r="F8" s="286"/>
+      <c r="G8" s="286"/>
+      <c r="H8" s="287"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="286" t="s">
+      <c r="B9" s="290" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="287"/>
-      <c r="D9" s="293" t="s">
+      <c r="C9" s="291"/>
+      <c r="D9" s="297" t="s">
         <v>206</v>
       </c>
-      <c r="E9" s="294"/>
-      <c r="F9" s="294"/>
-      <c r="G9" s="294"/>
-      <c r="H9" s="295"/>
-    </row>
-    <row r="10" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B10" s="288" t="s">
+      <c r="E9" s="298"/>
+      <c r="F9" s="298"/>
+      <c r="G9" s="298"/>
+      <c r="H9" s="299"/>
+    </row>
+    <row r="10" spans="2:14" ht="13.5" thickBot="1">
+      <c r="B10" s="292" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="289"/>
-      <c r="D10" s="296" t="s">
+      <c r="C10" s="293"/>
+      <c r="D10" s="300" t="s">
         <v>200</v>
       </c>
-      <c r="E10" s="297"/>
-      <c r="F10" s="297"/>
-      <c r="G10" s="297"/>
-      <c r="H10" s="298"/>
-    </row>
-    <row r="11" spans="2:14" ht="14.25" thickBot="1"/>
-    <row r="12" spans="2:14" ht="14.25" thickBot="1">
+      <c r="E10" s="301"/>
+      <c r="F10" s="301"/>
+      <c r="G10" s="301"/>
+      <c r="H10" s="302"/>
+    </row>
+    <row r="11" spans="2:14" ht="13.5" thickBot="1"/>
+    <row r="12" spans="2:14" ht="13.5" thickBot="1">
       <c r="B12" s="134" t="s">
         <v>33</v>
       </c>
@@ -12983,7 +13056,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="14.25" thickTop="1">
+    <row r="13" spans="2:14" ht="13.5" thickTop="1">
       <c r="B13" s="102">
         <v>1</v>
       </c>
@@ -12994,15 +13067,15 @@
         <v>47</v>
       </c>
       <c r="E13" s="195" t="s">
-        <v>242</v>
+        <v>284</v>
       </c>
       <c r="F13" s="47" t="str">
         <f t="shared" ref="F13:F37" ca="1" si="0">IF($D13&lt;&gt;"","u4_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"Srcchk","")</f>
         <v>u4_s_AlertC_avswarSrcchk</v>
       </c>
       <c r="G13" s="47" t="str">
-        <f t="shared" ref="G13:G37" ca="1" si="1">IF($D13&lt;&gt;"",IF($E13="○","vd_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"RwTx","NULL"),"")</f>
-        <v>vd_s_AlertC_avswarRwTx</v>
+        <f t="shared" ref="G13:G37" si="1">IF($D13&lt;&gt;"",IF($E13="○","vd_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"RwTx","NULL"),"")</f>
+        <v>NULL</v>
       </c>
       <c r="H13" s="106" t="str">
         <f ca="1">IF($D13&lt;&gt;"","ALERT_CH_"&amp;UPPER($D$6)&amp;IF($D$7=1,"","_"&amp;UPPER($C13)),"")</f>
@@ -13836,7 +13909,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="14.25" thickBot="1">
+    <row r="37" spans="2:14" ht="13.5" thickBot="1">
       <c r="B37" s="93">
         <v>25</v>
       </c>
@@ -13935,21 +14008,21 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B2:R59"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="36.5" customWidth="1"/>
-    <col min="6" max="6" width="71.125" customWidth="1"/>
-    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="3.875" customWidth="1"/>
-    <col min="16" max="16" width="9.875" customWidth="1"/>
-    <col min="17" max="17" width="44.625" customWidth="1"/>
-    <col min="18" max="18" width="73.625" customWidth="1"/>
+    <col min="5" max="5" width="36.453125" customWidth="1"/>
+    <col min="6" max="6" width="71.08984375" customWidth="1"/>
+    <col min="7" max="7" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="15" width="3.90625" customWidth="1"/>
+    <col min="16" max="16" width="9.90625" customWidth="1"/>
+    <col min="17" max="17" width="44.6328125" customWidth="1"/>
+    <col min="18" max="18" width="73.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="14.25" thickBot="1">
+    <row r="2" spans="2:18" ht="13.5" thickBot="1">
       <c r="B2" t="s">
         <v>192</v>
       </c>
@@ -13957,7 +14030,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="14.25" thickBot="1">
+    <row r="3" spans="2:18" ht="13.5" thickBot="1">
       <c r="B3" s="134" t="s">
         <v>33</v>
       </c>
@@ -13995,7 +14068,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="14.25" hidden="1" thickTop="1">
+    <row r="4" spans="2:18" ht="13.5" hidden="1" thickTop="1">
       <c r="B4" s="166">
         <v>0</v>
       </c>
@@ -14023,7 +14096,7 @@
       </c>
       <c r="R4" s="133"/>
     </row>
-    <row r="5" spans="2:18" ht="122.25" thickTop="1">
+    <row r="5" spans="2:18" ht="117.5" thickTop="1">
       <c r="B5" s="169">
         <v>1</v>
       </c>
@@ -14031,14 +14104,14 @@
         <v>234</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E5" s="63" t="str">
         <f ca="1">IF($C5&lt;&gt;"","ALERT_" &amp; D5 &amp; "_ID_"&amp;UPPER(Matrix!$D$6) &amp; "_" &amp; $C5,"")</f>
         <v>ALERT_OPT_ID_C_AVSWAR_AVSEXT</v>
       </c>
       <c r="F5" s="239" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G5" s="63">
         <f ca="1">IF(E5&lt;&gt;"",LEN(E5),"")</f>
@@ -14557,7 +14630,7 @@
       <c r="Q28" s="138"/>
       <c r="R28" s="113"/>
     </row>
-    <row r="29" spans="2:18" ht="14.25" thickBot="1">
+    <row r="29" spans="2:18" ht="13.5" thickBot="1">
       <c r="B29" s="170">
         <v>25</v>
       </c>
@@ -14579,7 +14652,7 @@
       <c r="Q29" s="136"/>
       <c r="R29" s="115"/>
     </row>
-    <row r="32" spans="2:18" ht="14.25" thickBot="1">
+    <row r="32" spans="2:18" ht="13.5" thickBot="1">
       <c r="B32" t="s">
         <v>193</v>
       </c>
@@ -14587,7 +14660,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="14.25" thickBot="1">
+    <row r="33" spans="2:18" ht="13.5" thickBot="1">
       <c r="B33" s="134" t="s">
         <v>33</v>
       </c>
@@ -14619,7 +14692,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="14.25" hidden="1" thickTop="1">
+    <row r="34" spans="2:18" ht="13.5" hidden="1" thickTop="1">
       <c r="B34" s="166">
         <v>0</v>
       </c>
@@ -14645,7 +14718,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="14.25" thickTop="1">
+    <row r="35" spans="2:18" ht="13.5" thickTop="1">
       <c r="B35" s="169">
         <v>1</v>
       </c>
@@ -15173,7 +15246,7 @@
       <c r="Q58" s="138"/>
       <c r="R58" s="171"/>
     </row>
-    <row r="59" spans="2:18" ht="14.25" thickBot="1">
+    <row r="59" spans="2:18" ht="13.5" thickBot="1">
       <c r="B59" s="170">
         <v>25</v>
       </c>
@@ -15225,29 +15298,29 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:U103"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="28.375" customWidth="1"/>
-    <col min="3" max="3" width="15.875" customWidth="1"/>
-    <col min="5" max="5" width="12.375" customWidth="1"/>
-    <col min="6" max="6" width="25.75" customWidth="1"/>
-    <col min="7" max="7" width="12.375" customWidth="1"/>
-    <col min="8" max="8" width="29.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.375" customWidth="1"/>
-    <col min="10" max="10" width="62.5" customWidth="1"/>
-    <col min="11" max="11" width="12.375" customWidth="1"/>
-    <col min="12" max="12" width="16.125" customWidth="1"/>
-    <col min="14" max="14" width="30.125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="57.125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="28.36328125" customWidth="1"/>
+    <col min="3" max="3" width="15.90625" customWidth="1"/>
+    <col min="5" max="5" width="12.36328125" customWidth="1"/>
+    <col min="6" max="6" width="25.7265625" customWidth="1"/>
+    <col min="7" max="7" width="12.36328125" customWidth="1"/>
+    <col min="8" max="8" width="29.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.36328125" customWidth="1"/>
+    <col min="10" max="10" width="62.453125" customWidth="1"/>
+    <col min="11" max="11" width="12.36328125" customWidth="1"/>
+    <col min="12" max="12" width="16.08984375" customWidth="1"/>
+    <col min="14" max="14" width="30.08984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="57.08984375" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="14.25" thickBot="1">
+    <row r="1" spans="2:21" ht="13.5" thickBot="1">
       <c r="C1" s="86" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="14.25" thickBot="1">
+    <row r="2" spans="2:21" ht="13.5" thickBot="1">
       <c r="B2" s="94" t="s">
         <v>57</v>
       </c>
@@ -15291,7 +15364,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="15" hidden="1" thickTop="1" thickBot="1">
+    <row r="3" spans="2:21" ht="14" hidden="1" thickTop="1" thickBot="1">
       <c r="B3" s="24"/>
       <c r="C3" s="46" t="s">
         <v>107</v>
@@ -15312,12 +15385,12 @@
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="14.25" thickTop="1">
+    <row r="4" spans="2:21" ht="13.5" thickTop="1">
       <c r="B4" s="105" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C4" s="104" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D4" s="116">
         <v>0</v>
@@ -15344,7 +15417,7 @@
         <v>234</v>
       </c>
       <c r="L4" s="190" t="s">
-        <v>239</v>
+        <v>30</v>
       </c>
       <c r="M4" s="47">
         <f ca="1">LEN(N4)</f>
@@ -15367,7 +15440,7 @@
         <v>233</v>
       </c>
       <c r="C5" s="104" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D5" s="116">
         <v>1</v>
@@ -15602,7 +15675,7 @@
       </c>
       <c r="U12" s="26"/>
     </row>
-    <row r="13" spans="2:21" ht="14.25" thickBot="1">
+    <row r="13" spans="2:21" ht="13.5" thickBot="1">
       <c r="B13" s="24"/>
       <c r="C13" s="23"/>
       <c r="D13" s="112"/>
@@ -17853,7 +17926,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="2:15" ht="14.25" thickBot="1">
+    <row r="103" spans="2:15" ht="13.5" thickBot="1">
       <c r="B103" s="48"/>
       <c r="C103" s="49"/>
       <c r="D103" s="114"/>
@@ -17927,20 +18000,20 @@
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="6" style="183" customWidth="1"/>
-    <col min="2" max="2" width="16.75" style="183" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7265625" style="183" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3" style="183" bestFit="1" customWidth="1"/>
     <col min="4" max="35" width="3" style="183" customWidth="1"/>
-    <col min="36" max="36" width="36.375" style="183" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.125" style="183" customWidth="1"/>
+    <col min="36" max="36" width="36.36328125" style="183" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.08984375" style="183" customWidth="1"/>
     <col min="38" max="42" width="9" style="183" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="20.625" style="183" hidden="1" customWidth="1"/>
-    <col min="44" max="45" width="41.125" style="183" customWidth="1"/>
+    <col min="43" max="43" width="20.6328125" style="183" hidden="1" customWidth="1"/>
+    <col min="44" max="45" width="41.08984375" style="183" customWidth="1"/>
     <col min="46" max="46" width="37" style="183" customWidth="1"/>
-    <col min="47" max="47" width="41.125" style="183" customWidth="1"/>
-    <col min="48" max="48" width="23.625" style="183" customWidth="1"/>
+    <col min="47" max="47" width="41.08984375" style="183" customWidth="1"/>
+    <col min="48" max="48" width="23.6328125" style="183" customWidth="1"/>
     <col min="49" max="49" width="29" style="183" bestFit="1" customWidth="1"/>
     <col min="50" max="16384" width="9" style="183"/>
   </cols>
@@ -17957,7 +18030,7 @@
       <c r="B2" s="121" t="s">
         <v>122</v>
       </c>
-      <c r="C2" s="303" t="s">
+      <c r="C2" s="307" t="s">
         <v>83</v>
       </c>
       <c r="D2" s="53">
@@ -18056,7 +18129,7 @@
       <c r="AI2" s="53">
         <v>0</v>
       </c>
-      <c r="AJ2" s="305" t="s">
+      <c r="AJ2" s="309" t="s">
         <v>121</v>
       </c>
     </row>
@@ -18065,7 +18138,7 @@
         <f>IF(OR(IF(COUNTIF(D6:AC69,"0")&lt;&gt;0,TRUE,FALSE),IF(COUNTIF(D6:AC69,"1")&lt;&gt;0,TRUE,FALSE)),"Search Table","Index Table")</f>
         <v>Index Table</v>
       </c>
-      <c r="C3" s="304"/>
+      <c r="C3" s="308"/>
       <c r="D3" s="123" t="s">
         <v>60</v>
       </c>
@@ -18147,25 +18220,25 @@
       <c r="AD3" s="124" t="s">
         <v>61</v>
       </c>
-      <c r="AE3" s="307" t="s">
-        <v>244</v>
-      </c>
-      <c r="AF3" s="309"/>
-      <c r="AG3" s="307" t="s">
-        <v>243</v>
-      </c>
-      <c r="AH3" s="308"/>
-      <c r="AI3" s="309"/>
-      <c r="AJ3" s="306"/>
+      <c r="AE3" s="311" t="s">
+        <v>242</v>
+      </c>
+      <c r="AF3" s="313"/>
+      <c r="AG3" s="311" t="s">
+        <v>241</v>
+      </c>
+      <c r="AH3" s="312"/>
+      <c r="AI3" s="313"/>
+      <c r="AJ3" s="310"/>
       <c r="AR3" s="87" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="14.25" thickBot="1">
-      <c r="A4" s="299" t="s">
+    <row r="4" spans="1:49" ht="13.5" thickBot="1">
+      <c r="A4" s="303" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="300"/>
+      <c r="B4" s="304"/>
       <c r="C4" s="184"/>
       <c r="D4" s="184"/>
       <c r="E4" s="184"/>
@@ -18209,9 +18282,9 @@
       <c r="AV4" s="76"/>
       <c r="AW4" s="77"/>
     </row>
-    <row r="5" spans="1:49" ht="14.25" thickBot="1">
-      <c r="A5" s="301"/>
-      <c r="B5" s="302"/>
+    <row r="5" spans="1:49" ht="13.5" thickBot="1">
+      <c r="A5" s="305"/>
+      <c r="B5" s="306"/>
       <c r="C5" s="185"/>
       <c r="D5" s="185"/>
       <c r="E5" s="185"/>
@@ -18374,7 +18447,7 @@
         <v>0</v>
       </c>
       <c r="AJ6" s="103" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AL6" s="183" t="str">
         <f t="shared" ref="AL6:AL69" si="0">IF($AJ6="UNKNOWN","    (U1)ALERT_REQ_UNKNOWN","    (U1)"&amp;"ALERT_REQ_"&amp;$AW$17&amp;"_"&amp;IF($AW$6&lt;&gt;$AW$17,$AW$6&amp;"_","")&amp;AJ6)</f>
@@ -18506,7 +18579,7 @@
         <v>1</v>
       </c>
       <c r="AJ7" s="103" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AL7" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18639,7 +18712,7 @@
         <v>0</v>
       </c>
       <c r="AJ8" s="103" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AL8" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18659,7 +18732,7 @@
       </c>
       <c r="AU8" s="58" t="str">
         <f ca="1">IF($AW$15&lt;&gt;"NULL","        &amp;"&amp;$AW$15&amp;","&amp;REPT(" ",69-LEN($AW$15))&amp;"/* fp_vd_XDST                                         */","        vdp_PTR_NA,                                                            /* fp_vd_XDST                                         */")</f>
-        <v xml:space="preserve">        &amp;vd_s_AlertC_avswarRwTx,                                               /* fp_vd_XDST                                         */</v>
+        <v xml:space="preserve">        vdp_PTR_NA,                                                            /* fp_vd_XDST                                         */</v>
       </c>
       <c r="AV8" s="44" t="s">
         <v>71</v>
@@ -18772,7 +18845,7 @@
         <v>1</v>
       </c>
       <c r="AJ9" s="103" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AL9" s="183" t="str">
         <f t="shared" si="0"/>
@@ -18902,7 +18975,7 @@
         <v>0</v>
       </c>
       <c r="AJ10" s="103" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AL10" s="183" t="str">
         <f t="shared" si="0"/>
@@ -19035,7 +19108,7 @@
         <v>1</v>
       </c>
       <c r="AJ11" s="103" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AL11" s="183" t="str">
         <f t="shared" si="0"/>
@@ -19168,7 +19241,7 @@
         <v>0</v>
       </c>
       <c r="AJ12" s="103" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AL12" s="183" t="str">
         <f t="shared" si="0"/>
@@ -19298,7 +19371,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" s="103" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AL13" s="183" t="str">
         <f t="shared" si="0"/>
@@ -19431,7 +19504,7 @@
         <v>0</v>
       </c>
       <c r="AJ14" s="103" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AL14" s="183" t="str">
         <f t="shared" si="0"/>
@@ -19564,7 +19637,7 @@
         <v>1</v>
       </c>
       <c r="AJ15" s="103" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AL15" s="183" t="str">
         <f t="shared" si="0"/>
@@ -19591,7 +19664,7 @@
       </c>
       <c r="AW15" s="63" t="str">
         <f ca="1">IF(AW6&lt;&gt;AW17,VLOOKUP(AW6,Matrix!$C$13:$G$37,5,FALSE),Matrix!G13)</f>
-        <v>vd_s_AlertC_avswarRwTx</v>
+        <v>NULL</v>
       </c>
     </row>
     <row r="16" spans="1:49">
@@ -19697,7 +19770,7 @@
         <v>0</v>
       </c>
       <c r="AJ16" s="103" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AL16" s="183" t="str">
         <f t="shared" si="0"/>
@@ -19726,7 +19799,7 @@
         <v>ALERT_VOM_IGN_ON</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="14.25" thickBot="1">
+    <row r="17" spans="2:49" ht="13.5" thickBot="1">
       <c r="B17" s="130"/>
       <c r="C17" s="42">
         <f t="shared" si="2"/>
@@ -19829,7 +19902,7 @@
         <v>1</v>
       </c>
       <c r="AJ17" s="103" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AL17" s="183" t="str">
         <f t="shared" si="0"/>
@@ -19961,7 +20034,7 @@
         <v>0</v>
       </c>
       <c r="AJ18" s="103" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AL18" s="183" t="str">
         <f t="shared" si="0"/>
@@ -20083,7 +20156,7 @@
         <v>1</v>
       </c>
       <c r="AJ19" s="103" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AL19" s="183" t="str">
         <f t="shared" si="0"/>
@@ -20205,7 +20278,7 @@
         <v>0</v>
       </c>
       <c r="AJ20" s="103" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AL20" s="183" t="str">
         <f t="shared" si="0"/>
@@ -20327,7 +20400,7 @@
         <v>1</v>
       </c>
       <c r="AJ21" s="103" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AL21" s="183" t="str">
         <f t="shared" si="0"/>
@@ -20449,7 +20522,7 @@
         <v>0</v>
       </c>
       <c r="AJ22" s="103" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AL22" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20571,7 +20644,7 @@
         <v>1</v>
       </c>
       <c r="AJ23" s="103" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AL23" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20693,7 +20766,7 @@
         <v>0</v>
       </c>
       <c r="AJ24" s="103" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AL24" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20815,7 +20888,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" s="103" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AL25" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20937,7 +21010,7 @@
         <v>0</v>
       </c>
       <c r="AJ26" s="103" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AL26" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21059,7 +21132,7 @@
         <v>1</v>
       </c>
       <c r="AJ27" s="103" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AL27" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21181,7 +21254,7 @@
         <v>0</v>
       </c>
       <c r="AJ28" s="103" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AL28" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21303,7 +21376,7 @@
         <v>1</v>
       </c>
       <c r="AJ29" s="103" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AL29" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21425,7 +21498,7 @@
         <v>0</v>
       </c>
       <c r="AJ30" s="103" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AL30" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21547,7 +21620,7 @@
         <v>1</v>
       </c>
       <c r="AJ31" s="103" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AL31" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21669,7 +21742,7 @@
         <v>0</v>
       </c>
       <c r="AJ32" s="103" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AL32" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21791,7 +21864,7 @@
         <v>1</v>
       </c>
       <c r="AJ33" s="103" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AL33" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21913,7 +21986,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="103" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AL34" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22035,7 +22108,7 @@
         <v>1</v>
       </c>
       <c r="AJ35" s="103" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AL35" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22157,7 +22230,7 @@
         <v>0</v>
       </c>
       <c r="AJ36" s="103" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AL36" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22279,7 +22352,7 @@
         <v>1</v>
       </c>
       <c r="AJ37" s="103" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AL37" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -26138,7 +26211,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="14.25" thickBot="1">
+    <row r="70" spans="1:46" ht="13.5" thickBot="1">
       <c r="A70" s="51" t="s">
         <v>63</v>
       </c>
@@ -46766,22 +46839,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:CY117"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="71.875" customWidth="1"/>
-    <col min="3" max="10" width="3.375" customWidth="1"/>
-    <col min="11" max="11" width="19.75" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="26.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.90625" customWidth="1"/>
+    <col min="3" max="10" width="3.36328125" customWidth="1"/>
+    <col min="11" max="11" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.26953125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="20" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.125" customWidth="1"/>
-    <col min="15" max="15" width="29.25" customWidth="1"/>
+    <col min="14" max="14" width="17.08984375" customWidth="1"/>
+    <col min="15" max="15" width="29.26953125" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="10.875" customWidth="1"/>
+    <col min="17" max="17" width="10.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="15" thickBot="1">
+    <row r="2" spans="2:17" ht="14.5" thickBot="1">
       <c r="B2" s="243" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C2" s="183"/>
       <c r="D2" s="183"/>
@@ -46799,20 +46872,20 @@
       <c r="P2" s="183"/>
       <c r="Q2" s="183"/>
     </row>
-    <row r="3" spans="2:17" ht="15" thickBot="1">
+    <row r="3" spans="2:17" ht="14.5" thickBot="1">
       <c r="B3" s="91" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="310" t="s">
+      <c r="C3" s="314" t="s">
         <v>201</v>
       </c>
-      <c r="D3" s="311"/>
-      <c r="E3" s="311"/>
-      <c r="F3" s="311"/>
-      <c r="G3" s="311"/>
-      <c r="H3" s="311"/>
-      <c r="I3" s="311"/>
-      <c r="J3" s="312"/>
+      <c r="D3" s="315"/>
+      <c r="E3" s="315"/>
+      <c r="F3" s="315"/>
+      <c r="G3" s="315"/>
+      <c r="H3" s="315"/>
+      <c r="I3" s="315"/>
+      <c r="J3" s="316"/>
       <c r="K3" s="162"/>
       <c r="L3" s="162"/>
       <c r="M3" s="165"/>
@@ -46849,22 +46922,22 @@
       <c r="B5" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="313" t="s">
+      <c r="C5" s="317" t="s">
         <v>170</v>
       </c>
-      <c r="D5" s="314"/>
-      <c r="E5" s="314"/>
-      <c r="F5" s="314"/>
-      <c r="G5" s="314"/>
-      <c r="H5" s="314"/>
-      <c r="I5" s="314"/>
-      <c r="J5" s="315"/>
+      <c r="D5" s="318"/>
+      <c r="E5" s="318"/>
+      <c r="F5" s="318"/>
+      <c r="G5" s="318"/>
+      <c r="H5" s="318"/>
+      <c r="I5" s="318"/>
+      <c r="J5" s="319"/>
       <c r="K5" s="218" t="s">
         <v>228</v>
       </c>
       <c r="L5" s="219"/>
       <c r="M5" s="26" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="N5" s="71" t="s">
         <v>22</v>
@@ -46879,7 +46952,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="40.5">
+    <row r="6" spans="2:17" ht="39">
       <c r="B6" s="66" t="s">
         <v>32</v>
       </c>
@@ -46920,38 +46993,38 @@
       <c r="O6" s="35"/>
       <c r="P6" s="72"/>
       <c r="Q6" s="85" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="7" spans="2:17" ht="27">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" ht="26">
       <c r="B7" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="316" t="s">
+      <c r="C7" s="320" t="s">
         <v>150</v>
       </c>
-      <c r="D7" s="314"/>
-      <c r="E7" s="314"/>
-      <c r="F7" s="314"/>
-      <c r="G7" s="314"/>
-      <c r="H7" s="314"/>
-      <c r="I7" s="314"/>
-      <c r="J7" s="315"/>
+      <c r="D7" s="318"/>
+      <c r="E7" s="318"/>
+      <c r="F7" s="318"/>
+      <c r="G7" s="318"/>
+      <c r="H7" s="318"/>
+      <c r="I7" s="318"/>
+      <c r="J7" s="319"/>
       <c r="K7" s="222" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="L7" s="222" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="M7" s="27"/>
       <c r="N7" s="72"/>
       <c r="O7" s="35"/>
       <c r="P7" s="72"/>
       <c r="Q7" s="69" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="8" spans="2:17" ht="136.5">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" ht="131">
       <c r="B8" s="66" t="s">
         <v>27</v>
       </c>
@@ -46980,10 +47053,10 @@
         <v>160</v>
       </c>
       <c r="K8" s="222" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="L8" s="222" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="M8" s="26" t="s">
         <v>28</v>
@@ -46992,7 +47065,7 @@
       <c r="O8" s="35"/>
       <c r="P8" s="72"/>
       <c r="Q8" s="69" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" spans="2:17" ht="154.5" customHeight="1" thickBot="1">
@@ -47024,26 +47097,26 @@
         <v>162</v>
       </c>
       <c r="K9" s="223" t="s">
+        <v>248</v>
+      </c>
+      <c r="L9" s="224" t="s">
+        <v>265</v>
+      </c>
+      <c r="M9" s="28" t="s">
         <v>250</v>
-      </c>
-      <c r="L9" s="224" t="s">
-        <v>267</v>
-      </c>
-      <c r="M9" s="28" t="s">
-        <v>252</v>
       </c>
       <c r="N9" s="70"/>
       <c r="O9" s="241" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P9" s="70"/>
       <c r="Q9" s="240" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="10" spans="2:17" ht="14.25" thickTop="1">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" ht="13.5" thickTop="1">
       <c r="B10" s="235" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C10" s="159" t="s">
         <v>161</v>
@@ -47073,7 +47146,7 @@
         <v>204</v>
       </c>
       <c r="L10" s="226" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M10" s="227" t="s">
         <v>107</v>
@@ -47089,7 +47162,7 @@
     </row>
     <row r="11" spans="2:17">
       <c r="B11" s="236" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C11" s="159" t="s">
         <v>161</v>
@@ -47116,26 +47189,26 @@
         <v>161</v>
       </c>
       <c r="K11" s="217" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="L11" s="228" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M11" s="31" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="N11" s="233"/>
       <c r="O11" s="232" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="P11" s="233"/>
       <c r="Q11" s="228" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" spans="2:17">
       <c r="B12" s="236" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C12" s="159" t="s">
         <v>161</v>
@@ -47162,17 +47235,17 @@
         <v>161</v>
       </c>
       <c r="K12" s="217" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="L12" s="228" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="M12" s="30" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="N12" s="36"/>
       <c r="O12" s="232" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="P12" s="36"/>
       <c r="Q12" s="228" t="s">
@@ -47181,7 +47254,7 @@
     </row>
     <row r="13" spans="2:17">
       <c r="B13" s="236" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C13" s="160" t="s">
         <v>161</v>
@@ -47208,10 +47281,10 @@
         <v>161</v>
       </c>
       <c r="K13" s="217" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="L13" s="228" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="M13" s="30" t="s">
         <v>31</v>
@@ -47227,7 +47300,7 @@
     </row>
     <row r="14" spans="2:17" s="183" customFormat="1">
       <c r="B14" s="236" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C14" s="160" t="s">
         <v>161</v>
@@ -47254,10 +47327,10 @@
         <v>161</v>
       </c>
       <c r="K14" s="238" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="L14" s="228" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="M14" s="30" t="s">
         <v>31</v>
@@ -47273,7 +47346,7 @@
     </row>
     <row r="15" spans="2:17" s="183" customFormat="1">
       <c r="B15" s="236" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C15" s="160" t="s">
         <v>161</v>
@@ -47303,23 +47376,23 @@
         <v>207</v>
       </c>
       <c r="L15" s="228" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="M15" s="31" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="N15" s="36"/>
       <c r="O15" s="232" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="P15" s="36"/>
       <c r="Q15" s="228" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="16" spans="2:17" s="183" customFormat="1">
       <c r="B16" s="236" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C16" s="160" t="s">
         <v>161</v>
@@ -47349,21 +47422,21 @@
         <v>208</v>
       </c>
       <c r="L16" s="228" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="M16" s="31" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="N16" s="36"/>
       <c r="O16" s="232" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="P16" s="36"/>
       <c r="Q16" s="228" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="17" spans="2:61" ht="14.25" thickBot="1">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="17" spans="2:61" ht="13.5" thickBot="1">
       <c r="B17" s="21" t="s">
         <v>232</v>
       </c>
@@ -48487,16 +48560,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:D27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="9" style="183"/>
-    <col min="2" max="2" width="4.875" style="183" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.25" style="183" customWidth="1"/>
+    <col min="2" max="2" width="4.90625" style="183" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" style="183" customWidth="1"/>
     <col min="4" max="4" width="86" style="183" customWidth="1"/>
     <col min="5" max="16384" width="9" style="183"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="14.25" thickBot="1">
+    <row r="2" spans="2:4" ht="13.5" thickBot="1">
       <c r="B2" s="79" t="s">
         <v>84</v>
       </c>
@@ -48506,7 +48579,7 @@
       </c>
       <c r="D2" s="80"/>
     </row>
-    <row r="3" spans="2:4" ht="14.25" thickBot="1">
+    <row r="3" spans="2:4" ht="13.5" thickBot="1">
       <c r="B3" s="73" t="s">
         <v>84</v>
       </c>
@@ -48517,7 +48590,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="14.25" thickTop="1">
+    <row r="4" spans="2:4" ht="13.5" thickTop="1">
       <c r="B4" s="12">
         <v>0</v>
       </c>
@@ -48528,7 +48601,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="40.5">
+    <row r="5" spans="2:4" ht="39">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -48539,7 +48612,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="27">
+    <row r="6" spans="2:4" ht="26">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -48550,7 +48623,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="54">
+    <row r="7" spans="2:4" ht="52">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -48561,7 +48634,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="81">
+    <row r="8" spans="2:4" ht="78">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -48583,7 +48656,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="27">
+    <row r="10" spans="2:4" ht="26">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -48594,7 +48667,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="27">
+    <row r="11" spans="2:4" ht="26">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -48605,7 +48678,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="27">
+    <row r="12" spans="2:4" ht="26">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -48616,7 +48689,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="27">
+    <row r="13" spans="2:4" ht="26">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -48627,7 +48700,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="27">
+    <row r="14" spans="2:4" ht="26">
       <c r="B14" s="2">
         <v>10</v>
       </c>
@@ -48638,7 +48711,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="135">
+    <row r="15" spans="2:4" ht="130">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -48660,7 +48733,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="27">
+    <row r="17" spans="2:4" ht="26">
       <c r="B17" s="2">
         <v>13</v>
       </c>
@@ -48671,7 +48744,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="67.5">
+    <row r="18" spans="2:4" ht="91">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -48682,7 +48755,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="40.5">
+    <row r="19" spans="2:4" ht="39">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -48715,7 +48788,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="27">
+    <row r="22" spans="2:4" ht="26">
       <c r="B22" s="2">
         <v>18</v>
       </c>
@@ -48726,7 +48799,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="27">
+    <row r="23" spans="2:4" ht="26">
       <c r="B23" s="2">
         <v>19</v>
       </c>
@@ -48737,7 +48810,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="24" spans="2:4" ht="94.5">
+    <row r="24" spans="2:4" ht="91">
       <c r="B24" s="2">
         <v>20</v>
       </c>
@@ -48758,7 +48831,7 @@
       <c r="C26" s="83"/>
       <c r="D26" s="69"/>
     </row>
-    <row r="27" spans="2:4" ht="14.25" thickBot="1">
+    <row r="27" spans="2:4" ht="13.5" thickBot="1">
       <c r="B27" s="3"/>
       <c r="C27" s="84"/>
       <c r="D27" s="5"/>

--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_C_AVSWAR-CSTD-A0-03-A-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_C_AVSWAR-CSTD-A0-03-A-C0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_JPlaptop\BEV_MCU\git_v043_AlertFix\src\PE1VM1\App\MET\IpcApplication\Vom\Alert\matrix\scc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\ソフトチーム\20260106_REMWAR_RW\045\IpcApplication\Vom\Alert\matrix\scc\ref更新\IpcApplication\Vom\Alert\matrix\scc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA66049-F0D0-4167-A311-C506B7E6DF0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3EDE930-F886-499B-8F19-5C1FDECE1B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14265" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="22740" windowHeight="14070" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙（承認）" sheetId="16" r:id="rId1"/>
@@ -603,7 +603,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2452" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2451" uniqueCount="286">
   <si>
     <t>更新履歴</t>
     <phoneticPr fontId="2"/>
@@ -2708,9 +2708,6 @@
   </si>
   <si>
     <t>AVSEXT</t>
-  </si>
-  <si>
-    <t>AVSEXT</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -2722,20 +2719,6 @@
   </si>
   <si>
     <t>C_AVSWAR-CSTD-A0-MEF01-REQ03-</t>
-  </si>
-  <si>
-    <t>OPT</t>
-  </si>
-  <si>
-    <t>以下の条件成立時に、機能“有”と判定する。
-&lt;AVS&gt;
-AND ┬ IGR(IG2) = ON
-　　└ AVSEXT = 001bを4.2s間で2回以上連続受信
-以下の条件成立時に、機能“無”と判定する。
-&lt;AVS&gt;
-AND ┬ IGR(IG2) = ON
-　　└ AVSEXT = 001b以外を4.2s間で2回以上連続受信</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>AVSMINF</t>
@@ -3002,6 +2985,23 @@
     </rPh>
     <rPh sb="13" eb="15">
       <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1.1.0</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>RWの削除
+[Config_IF]シート
+ALERT_OPT_ID_C_AVSWAR_AVSEXT
+削除</t>
+    <rPh sb="3" eb="5">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>サクジョ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4520,7 +4520,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="322">
+  <cellXfs count="325">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5259,23 +5259,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="27" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5337,6 +5349,45 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -5364,31 +5415,10 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="68" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -5398,24 +5428,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="50" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -5471,9 +5483,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -8538,8 +8547,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="36309300" y="6448425"/>
-          <a:ext cx="13783332" cy="9418270"/>
+          <a:off x="40173088" y="6633882"/>
+          <a:ext cx="15413601" cy="9777419"/>
           <a:chOff x="40173088" y="6633882"/>
           <a:chExt cx="15413601" cy="9777419"/>
         </a:xfrm>
@@ -9719,6 +9728,279 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6960DE4-A07A-43E0-91C0-EAA65997CC01}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18216563" y="881063"/>
+          <a:ext cx="833437" cy="5929312"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>459441</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>246529</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>85444</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>123265</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFC0208D-05E5-4D49-9995-837EF040E63F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="33796941" y="1994647"/>
+          <a:ext cx="3727356" cy="1613647"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>74</xdr:col>
+      <xdr:colOff>500062</xdr:colOff>
+      <xdr:row>113</xdr:row>
+      <xdr:rowOff>71437</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC2253A5-7F04-4F8D-9E89-8077A91DF65B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="39766875" y="16644938"/>
+          <a:ext cx="19145250" cy="6238874"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -10040,9 +10322,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B67217F-73C6-4474-923D-65746D362F67}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:AN49"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="40" width="2.26953125" style="203" customWidth="1"/>
+    <col min="1" max="40" width="2.25" style="203" customWidth="1"/>
     <col min="41" max="16384" width="9" style="203"/>
   </cols>
   <sheetData>
@@ -10383,91 +10665,91 @@
       <c r="AN8" s="206"/>
     </row>
     <row r="9" spans="1:40" ht="28.5" customHeight="1">
-      <c r="A9" s="257" t="str">
+      <c r="A9" s="261" t="str">
         <f ca="1">MID(CELL("filename",A1), FIND("[",CELL("filename",A1))+1, FIND("]",CELL("filename",A1))-FIND("[",CELL("filename",A1))-6)</f>
         <v>alert_C_AVSWAR-CSTD-A0-03-A-C0</v>
       </c>
-      <c r="B9" s="258"/>
-      <c r="C9" s="258"/>
-      <c r="D9" s="258"/>
-      <c r="E9" s="258"/>
-      <c r="F9" s="258"/>
-      <c r="G9" s="258"/>
-      <c r="H9" s="258"/>
-      <c r="I9" s="258"/>
-      <c r="J9" s="258"/>
-      <c r="K9" s="258"/>
-      <c r="L9" s="258"/>
-      <c r="M9" s="258"/>
-      <c r="N9" s="258"/>
-      <c r="O9" s="258"/>
-      <c r="P9" s="258"/>
-      <c r="Q9" s="258"/>
-      <c r="R9" s="258"/>
-      <c r="S9" s="258"/>
-      <c r="T9" s="258"/>
-      <c r="U9" s="258"/>
-      <c r="V9" s="258"/>
-      <c r="W9" s="258"/>
-      <c r="X9" s="258"/>
-      <c r="Y9" s="258"/>
-      <c r="Z9" s="258"/>
-      <c r="AA9" s="258"/>
-      <c r="AB9" s="258"/>
-      <c r="AC9" s="258"/>
-      <c r="AD9" s="258"/>
-      <c r="AE9" s="258"/>
-      <c r="AF9" s="258"/>
-      <c r="AG9" s="258"/>
-      <c r="AH9" s="258"/>
-      <c r="AI9" s="258"/>
-      <c r="AJ9" s="258"/>
-      <c r="AK9" s="258"/>
-      <c r="AL9" s="258"/>
-      <c r="AM9" s="258"/>
-      <c r="AN9" s="259"/>
+      <c r="B9" s="262"/>
+      <c r="C9" s="262"/>
+      <c r="D9" s="262"/>
+      <c r="E9" s="262"/>
+      <c r="F9" s="262"/>
+      <c r="G9" s="262"/>
+      <c r="H9" s="262"/>
+      <c r="I9" s="262"/>
+      <c r="J9" s="262"/>
+      <c r="K9" s="262"/>
+      <c r="L9" s="262"/>
+      <c r="M9" s="262"/>
+      <c r="N9" s="262"/>
+      <c r="O9" s="262"/>
+      <c r="P9" s="262"/>
+      <c r="Q9" s="262"/>
+      <c r="R9" s="262"/>
+      <c r="S9" s="262"/>
+      <c r="T9" s="262"/>
+      <c r="U9" s="262"/>
+      <c r="V9" s="262"/>
+      <c r="W9" s="262"/>
+      <c r="X9" s="262"/>
+      <c r="Y9" s="262"/>
+      <c r="Z9" s="262"/>
+      <c r="AA9" s="262"/>
+      <c r="AB9" s="262"/>
+      <c r="AC9" s="262"/>
+      <c r="AD9" s="262"/>
+      <c r="AE9" s="262"/>
+      <c r="AF9" s="262"/>
+      <c r="AG9" s="262"/>
+      <c r="AH9" s="262"/>
+      <c r="AI9" s="262"/>
+      <c r="AJ9" s="262"/>
+      <c r="AK9" s="262"/>
+      <c r="AL9" s="262"/>
+      <c r="AM9" s="262"/>
+      <c r="AN9" s="263"/>
     </row>
     <row r="10" spans="1:40" ht="28.5" customHeight="1">
-      <c r="A10" s="257"/>
-      <c r="B10" s="258"/>
-      <c r="C10" s="258"/>
-      <c r="D10" s="258"/>
-      <c r="E10" s="258"/>
-      <c r="F10" s="258"/>
-      <c r="G10" s="258"/>
-      <c r="H10" s="258"/>
-      <c r="I10" s="258"/>
-      <c r="J10" s="258"/>
-      <c r="K10" s="258"/>
-      <c r="L10" s="258"/>
-      <c r="M10" s="258"/>
-      <c r="N10" s="258"/>
-      <c r="O10" s="258"/>
-      <c r="P10" s="258"/>
-      <c r="Q10" s="258"/>
-      <c r="R10" s="258"/>
-      <c r="S10" s="258"/>
-      <c r="T10" s="258"/>
-      <c r="U10" s="258"/>
-      <c r="V10" s="258"/>
-      <c r="W10" s="258"/>
-      <c r="X10" s="258"/>
-      <c r="Y10" s="258"/>
-      <c r="Z10" s="258"/>
-      <c r="AA10" s="258"/>
-      <c r="AB10" s="258"/>
-      <c r="AC10" s="258"/>
-      <c r="AD10" s="258"/>
-      <c r="AE10" s="258"/>
-      <c r="AF10" s="258"/>
-      <c r="AG10" s="258"/>
-      <c r="AH10" s="258"/>
-      <c r="AI10" s="258"/>
-      <c r="AJ10" s="258"/>
-      <c r="AK10" s="258"/>
-      <c r="AL10" s="258"/>
-      <c r="AM10" s="258"/>
-      <c r="AN10" s="259"/>
+      <c r="A10" s="261"/>
+      <c r="B10" s="262"/>
+      <c r="C10" s="262"/>
+      <c r="D10" s="262"/>
+      <c r="E10" s="262"/>
+      <c r="F10" s="262"/>
+      <c r="G10" s="262"/>
+      <c r="H10" s="262"/>
+      <c r="I10" s="262"/>
+      <c r="J10" s="262"/>
+      <c r="K10" s="262"/>
+      <c r="L10" s="262"/>
+      <c r="M10" s="262"/>
+      <c r="N10" s="262"/>
+      <c r="O10" s="262"/>
+      <c r="P10" s="262"/>
+      <c r="Q10" s="262"/>
+      <c r="R10" s="262"/>
+      <c r="S10" s="262"/>
+      <c r="T10" s="262"/>
+      <c r="U10" s="262"/>
+      <c r="V10" s="262"/>
+      <c r="W10" s="262"/>
+      <c r="X10" s="262"/>
+      <c r="Y10" s="262"/>
+      <c r="Z10" s="262"/>
+      <c r="AA10" s="262"/>
+      <c r="AB10" s="262"/>
+      <c r="AC10" s="262"/>
+      <c r="AD10" s="262"/>
+      <c r="AE10" s="262"/>
+      <c r="AF10" s="262"/>
+      <c r="AG10" s="262"/>
+      <c r="AH10" s="262"/>
+      <c r="AI10" s="262"/>
+      <c r="AJ10" s="262"/>
+      <c r="AK10" s="262"/>
+      <c r="AL10" s="262"/>
+      <c r="AM10" s="262"/>
+      <c r="AN10" s="263"/>
     </row>
     <row r="11" spans="1:40" ht="13.5" customHeight="1">
       <c r="A11" s="204"/>
@@ -11125,7 +11407,7 @@
       <c r="W26" s="205"/>
       <c r="X26" s="205"/>
       <c r="Y26" s="143" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="Z26" s="205"/>
       <c r="AA26" s="205"/>
@@ -11168,27 +11450,27 @@
       <c r="V27" s="205"/>
       <c r="W27" s="205"/>
       <c r="X27" s="205"/>
-      <c r="Y27" s="254" t="s">
+      <c r="Y27" s="258" t="s">
         <v>216</v>
       </c>
-      <c r="Z27" s="255"/>
-      <c r="AA27" s="255"/>
-      <c r="AB27" s="255"/>
-      <c r="AC27" s="256"/>
-      <c r="AD27" s="254" t="s">
+      <c r="Z27" s="259"/>
+      <c r="AA27" s="259"/>
+      <c r="AB27" s="259"/>
+      <c r="AC27" s="260"/>
+      <c r="AD27" s="258" t="s">
         <v>217</v>
       </c>
-      <c r="AE27" s="255"/>
-      <c r="AF27" s="255"/>
-      <c r="AG27" s="255"/>
-      <c r="AH27" s="256"/>
-      <c r="AI27" s="260" t="s">
+      <c r="AE27" s="259"/>
+      <c r="AF27" s="259"/>
+      <c r="AG27" s="259"/>
+      <c r="AH27" s="260"/>
+      <c r="AI27" s="264" t="s">
         <v>218</v>
       </c>
-      <c r="AJ27" s="255"/>
-      <c r="AK27" s="255"/>
-      <c r="AL27" s="255"/>
-      <c r="AM27" s="256"/>
+      <c r="AJ27" s="259"/>
+      <c r="AK27" s="259"/>
+      <c r="AL27" s="259"/>
+      <c r="AM27" s="260"/>
       <c r="AN27" s="206"/>
     </row>
     <row r="28" spans="1:40" ht="13.5" customHeight="1">
@@ -11473,7 +11755,7 @@
       <c r="W34" s="205"/>
       <c r="X34" s="205"/>
       <c r="Y34" s="207" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="Z34" s="205"/>
       <c r="AA34" s="205"/>
@@ -11516,27 +11798,27 @@
       <c r="V35" s="205"/>
       <c r="W35" s="205"/>
       <c r="X35" s="205"/>
-      <c r="Y35" s="254" t="s">
+      <c r="Y35" s="258" t="s">
         <v>216</v>
       </c>
-      <c r="Z35" s="255"/>
-      <c r="AA35" s="255"/>
-      <c r="AB35" s="255"/>
-      <c r="AC35" s="256"/>
-      <c r="AD35" s="254" t="s">
+      <c r="Z35" s="259"/>
+      <c r="AA35" s="259"/>
+      <c r="AB35" s="259"/>
+      <c r="AC35" s="260"/>
+      <c r="AD35" s="258" t="s">
         <v>217</v>
       </c>
-      <c r="AE35" s="255"/>
-      <c r="AF35" s="255"/>
-      <c r="AG35" s="255"/>
-      <c r="AH35" s="256"/>
-      <c r="AI35" s="260" t="s">
+      <c r="AE35" s="259"/>
+      <c r="AF35" s="259"/>
+      <c r="AG35" s="259"/>
+      <c r="AH35" s="260"/>
+      <c r="AI35" s="264" t="s">
         <v>218</v>
       </c>
-      <c r="AJ35" s="255"/>
-      <c r="AK35" s="255"/>
-      <c r="AL35" s="255"/>
-      <c r="AM35" s="256"/>
+      <c r="AJ35" s="259"/>
+      <c r="AK35" s="259"/>
+      <c r="AL35" s="259"/>
+      <c r="AM35" s="260"/>
       <c r="AN35" s="206"/>
     </row>
     <row r="36" spans="1:40" ht="13.5" customHeight="1">
@@ -11866,27 +12148,27 @@
       <c r="V43" s="205"/>
       <c r="W43" s="205"/>
       <c r="X43" s="205"/>
-      <c r="Y43" s="254" t="s">
+      <c r="Y43" s="258" t="s">
         <v>216</v>
       </c>
-      <c r="Z43" s="255"/>
-      <c r="AA43" s="255"/>
-      <c r="AB43" s="255"/>
-      <c r="AC43" s="256"/>
-      <c r="AD43" s="254" t="s">
+      <c r="Z43" s="259"/>
+      <c r="AA43" s="259"/>
+      <c r="AB43" s="259"/>
+      <c r="AC43" s="260"/>
+      <c r="AD43" s="258" t="s">
         <v>217</v>
       </c>
-      <c r="AE43" s="255"/>
-      <c r="AF43" s="255"/>
-      <c r="AG43" s="255"/>
-      <c r="AH43" s="256"/>
-      <c r="AI43" s="254" t="s">
+      <c r="AE43" s="259"/>
+      <c r="AF43" s="259"/>
+      <c r="AG43" s="259"/>
+      <c r="AH43" s="260"/>
+      <c r="AI43" s="258" t="s">
         <v>218</v>
       </c>
-      <c r="AJ43" s="255"/>
-      <c r="AK43" s="255"/>
-      <c r="AL43" s="255"/>
-      <c r="AM43" s="256"/>
+      <c r="AJ43" s="259"/>
+      <c r="AK43" s="259"/>
+      <c r="AL43" s="259"/>
+      <c r="AM43" s="260"/>
       <c r="AN43" s="206"/>
     </row>
     <row r="44" spans="1:40" ht="13.5" customHeight="1">
@@ -12169,14 +12451,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:X13"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="4.453125" customWidth="1"/>
+    <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="9" style="9" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="69.453125" customWidth="1"/>
-    <col min="5" max="6" width="12.7265625" customWidth="1"/>
-    <col min="7" max="22" width="13.08984375" hidden="1" customWidth="1"/>
-    <col min="23" max="24" width="13.08984375" customWidth="1"/>
+    <col min="4" max="4" width="69.5" customWidth="1"/>
+    <col min="5" max="6" width="12.75" customWidth="1"/>
+    <col min="7" max="22" width="13.125" hidden="1" customWidth="1"/>
+    <col min="23" max="24" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:24" ht="25.5" customHeight="1">
@@ -12187,18 +12469,18 @@
       <c r="H2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="261" t="s">
+      <c r="I2" s="265" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="261"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="261"/>
-      <c r="M2" s="261"/>
-      <c r="N2" s="261"/>
-      <c r="O2" s="261"/>
-      <c r="P2" s="261"/>
-      <c r="Q2" s="261"/>
-      <c r="R2" s="261"/>
+      <c r="J2" s="265"/>
+      <c r="K2" s="265"/>
+      <c r="L2" s="265"/>
+      <c r="M2" s="265"/>
+      <c r="N2" s="265"/>
+      <c r="O2" s="265"/>
+      <c r="P2" s="265"/>
+      <c r="Q2" s="265"/>
+      <c r="R2" s="265"/>
     </row>
     <row r="3" spans="2:24" ht="25.5" customHeight="1">
       <c r="C3" s="6"/>
@@ -12211,25 +12493,25 @@
       <c r="H3" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="I3" s="262" t="s">
+      <c r="I3" s="266" t="s">
         <v>175</v>
       </c>
-      <c r="J3" s="263"/>
-      <c r="K3" s="263"/>
-      <c r="L3" s="263"/>
-      <c r="M3" s="263"/>
-      <c r="N3" s="263"/>
-      <c r="O3" s="263"/>
-      <c r="P3" s="263"/>
-      <c r="Q3" s="263"/>
-      <c r="R3" s="263"/>
+      <c r="J3" s="267"/>
+      <c r="K3" s="267"/>
+      <c r="L3" s="267"/>
+      <c r="M3" s="267"/>
+      <c r="N3" s="267"/>
+      <c r="O3" s="267"/>
+      <c r="P3" s="267"/>
+      <c r="Q3" s="267"/>
+      <c r="R3" s="267"/>
     </row>
     <row r="4" spans="2:24" ht="25.5" customHeight="1">
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="22" t="str">
         <f>DGET(B8:C14,"Ver.",H4:H5)</f>
-        <v>1.0.2</v>
+        <v>1.1.0</v>
       </c>
       <c r="F4" s="6"/>
       <c r="H4" s="9" t="s">
@@ -12243,45 +12525,45 @@
       <c r="F5" s="6"/>
       <c r="H5" s="11">
         <f>MAX(B9:B14)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="2:24" ht="13.5" thickBot="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:24" ht="14.25" thickBot="1"/>
     <row r="7" spans="2:24">
-      <c r="C7" s="266" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="267"/>
-      <c r="E7" s="268" t="s">
+      <c r="C7" s="270" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="271"/>
+      <c r="E7" s="272" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="268"/>
-      <c r="G7" s="269" t="s">
+      <c r="F7" s="272"/>
+      <c r="G7" s="273" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="269"/>
-      <c r="I7" s="269"/>
-      <c r="J7" s="269"/>
-      <c r="K7" s="269"/>
-      <c r="L7" s="269"/>
-      <c r="M7" s="270" t="s">
+      <c r="H7" s="273"/>
+      <c r="I7" s="273"/>
+      <c r="J7" s="273"/>
+      <c r="K7" s="273"/>
+      <c r="L7" s="273"/>
+      <c r="M7" s="274" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="270"/>
-      <c r="O7" s="270"/>
-      <c r="P7" s="270"/>
-      <c r="Q7" s="270"/>
-      <c r="R7" s="271"/>
-      <c r="S7" s="264" t="s">
+      <c r="N7" s="274"/>
+      <c r="O7" s="274"/>
+      <c r="P7" s="274"/>
+      <c r="Q7" s="274"/>
+      <c r="R7" s="275"/>
+      <c r="S7" s="268" t="s">
         <v>224</v>
       </c>
-      <c r="T7" s="264"/>
-      <c r="U7" s="264"/>
-      <c r="V7" s="264"/>
-      <c r="W7" s="264"/>
-      <c r="X7" s="265"/>
-    </row>
-    <row r="8" spans="2:24" ht="26.5" thickBot="1">
+      <c r="T7" s="268"/>
+      <c r="U7" s="268"/>
+      <c r="V7" s="268"/>
+      <c r="W7" s="268"/>
+      <c r="X7" s="269"/>
+    </row>
+    <row r="8" spans="2:24" ht="27.75" thickBot="1">
       <c r="B8" s="9" t="s">
         <v>91</v>
       </c>
@@ -12352,7 +12634,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:24" ht="13.5" thickTop="1">
+    <row r="9" spans="2:24" ht="14.25" thickTop="1">
       <c r="B9" s="9">
         <f>IF(C9=0,0,ROW()-ROW($B$8))</f>
         <v>1</v>
@@ -12424,16 +12706,16 @@
         <v>45275</v>
       </c>
     </row>
-    <row r="10" spans="2:24" ht="65">
+    <row r="10" spans="2:24" ht="67.5">
       <c r="B10" s="9">
         <f>IF(C10=0,0,ROW()-ROW($B$8))</f>
         <v>2</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D10" s="187" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>30</v>
@@ -12470,59 +12752,63 @@
       <c r="U10" s="1"/>
       <c r="V10" s="192"/>
       <c r="W10" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="X10" s="188">
         <v>45807</v>
       </c>
     </row>
-    <row r="11" spans="2:24" ht="91">
+    <row r="11" spans="2:24" ht="94.5">
       <c r="B11" s="9">
         <f>IF(C11=0,0,ROW()-ROW($B$8))</f>
         <v>3</v>
       </c>
-      <c r="C11" s="250" t="s">
-        <v>282</v>
-      </c>
-      <c r="D11" s="251" t="s">
-        <v>286</v>
-      </c>
-      <c r="E11" s="252" t="s">
+      <c r="C11" s="249" t="s">
+        <v>279</v>
+      </c>
+      <c r="D11" s="250" t="s">
+        <v>283</v>
+      </c>
+      <c r="E11" s="251" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="252" t="s">
+      <c r="F11" s="251" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="248"/>
-      <c r="S11" s="13"/>
-      <c r="T11" s="13"/>
-      <c r="U11" s="13"/>
-      <c r="V11" s="13"/>
-      <c r="W11" s="321" t="s">
-        <v>283</v>
-      </c>
-      <c r="X11" s="253">
+      <c r="G11" s="252"/>
+      <c r="H11" s="252"/>
+      <c r="I11" s="252"/>
+      <c r="J11" s="252"/>
+      <c r="K11" s="252"/>
+      <c r="L11" s="252"/>
+      <c r="M11" s="252"/>
+      <c r="N11" s="252"/>
+      <c r="O11" s="252"/>
+      <c r="P11" s="252"/>
+      <c r="Q11" s="252"/>
+      <c r="R11" s="253"/>
+      <c r="S11" s="254"/>
+      <c r="T11" s="254"/>
+      <c r="U11" s="254"/>
+      <c r="V11" s="254"/>
+      <c r="W11" s="252" t="s">
+        <v>280</v>
+      </c>
+      <c r="X11" s="255">
         <v>46008</v>
       </c>
     </row>
-    <row r="12" spans="2:24">
+    <row r="12" spans="2:24" ht="54">
       <c r="B12" s="9">
         <f>IF(C12=0,0,ROW()-ROW($B$8))</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="C12" s="256" t="s">
+        <v>284</v>
+      </c>
+      <c r="D12" s="257" t="s">
+        <v>285</v>
+      </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -12544,7 +12830,7 @@
       <c r="W12" s="13"/>
       <c r="X12" s="188"/>
     </row>
-    <row r="13" spans="2:24" ht="13.5" thickBot="1">
+    <row r="13" spans="2:24" ht="14.25" thickBot="1">
       <c r="B13" s="9">
         <f>IF(C13=0,0,ROW()-ROW($B$8))</f>
         <v>0</v>
@@ -12564,7 +12850,7 @@
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
-      <c r="R13" s="249"/>
+      <c r="R13" s="248"/>
       <c r="S13" s="4"/>
       <c r="T13" s="4"/>
       <c r="U13" s="4"/>
@@ -12598,11 +12884,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:E39"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="4.6328125" customWidth="1"/>
-    <col min="3" max="3" width="3.453125" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" customWidth="1"/>
+    <col min="2" max="2" width="4.625" customWidth="1"/>
+    <col min="3" max="3" width="3.5" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
     <col min="5" max="5" width="106" customWidth="1"/>
   </cols>
   <sheetData>
@@ -12616,13 +12902,13 @@
         <v>135</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="13.5" thickBot="1">
+    <row r="6" spans="2:5" ht="14.25" thickBot="1">
       <c r="B6" s="143" t="s">
         <v>126</v>
       </c>
       <c r="C6" s="143"/>
     </row>
-    <row r="7" spans="2:5" ht="13.5" thickBot="1">
+    <row r="7" spans="2:5" ht="14.25" thickBot="1">
       <c r="C7" s="73" t="s">
         <v>128</v>
       </c>
@@ -12647,7 +12933,7 @@
       <c r="D9" s="155"/>
       <c r="E9" s="154"/>
     </row>
-    <row r="10" spans="2:5" ht="13.5" thickBot="1">
+    <row r="10" spans="2:5" ht="14.25" thickBot="1">
       <c r="C10" s="151"/>
       <c r="D10" s="84"/>
       <c r="E10" s="5"/>
@@ -12655,14 +12941,14 @@
     <row r="11" spans="2:5">
       <c r="C11" s="149"/>
     </row>
-    <row r="12" spans="2:5" ht="13.5" thickBot="1">
+    <row r="12" spans="2:5" ht="14.25" thickBot="1">
       <c r="B12" s="144" t="s">
         <v>127</v>
       </c>
       <c r="C12" s="80"/>
       <c r="D12" s="80"/>
     </row>
-    <row r="13" spans="2:5" ht="13.5" thickBot="1">
+    <row r="13" spans="2:5" ht="14.25" thickBot="1">
       <c r="B13" s="145"/>
       <c r="C13" s="150" t="s">
         <v>128</v>
@@ -12674,7 +12960,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="13.5" thickTop="1">
+    <row r="14" spans="2:5" ht="14.25" thickTop="1">
       <c r="C14" s="147">
         <v>0</v>
       </c>
@@ -12751,17 +13037,17 @@
         <v>169</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="13.5" thickBot="1">
+    <row r="21" spans="2:5" ht="14.25" thickBot="1">
       <c r="C21" s="151"/>
       <c r="D21" s="84"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="24" spans="2:5" ht="13.5" thickBot="1">
+    <row r="24" spans="2:5" ht="14.25" thickBot="1">
       <c r="B24" s="143" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="13.5" thickBot="1">
+    <row r="25" spans="2:5" ht="14.25" thickBot="1">
       <c r="C25" s="150" t="s">
         <v>128</v>
       </c>
@@ -12848,26 +13134,26 @@
       <c r="D33" s="83"/>
       <c r="E33" s="69"/>
     </row>
-    <row r="34" spans="2:5" ht="13.5" thickBot="1">
+    <row r="34" spans="2:5" ht="14.25" thickBot="1">
       <c r="C34" s="151"/>
       <c r="D34" s="84"/>
       <c r="E34" s="5"/>
     </row>
-    <row r="37" spans="2:5" ht="13.5" thickBot="1">
+    <row r="37" spans="2:5" ht="14.25" thickBot="1">
       <c r="B37" s="143" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="38" spans="2:5">
-      <c r="C38" s="272"/>
-      <c r="D38" s="273"/>
+      <c r="C38" s="276"/>
+      <c r="D38" s="277"/>
       <c r="E38" s="108" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="13.5" thickBot="1">
-      <c r="C39" s="274"/>
-      <c r="D39" s="275"/>
+    <row r="39" spans="2:5" ht="14.25" thickBot="1">
+      <c r="C39" s="278"/>
+      <c r="D39" s="279"/>
       <c r="E39" s="5" t="s">
         <v>118</v>
       </c>
@@ -12895,133 +13181,133 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:N37"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="26.7265625" customWidth="1"/>
-    <col min="9" max="9" width="20.90625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="26.75" customWidth="1"/>
+    <col min="9" max="9" width="20.875" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="13.5" thickBot="1"/>
+    <row r="1" spans="2:14" ht="14.25" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="288" t="s">
+      <c r="B2" s="302" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="289"/>
-      <c r="D2" s="276" t="s">
-        <v>280</v>
-      </c>
-      <c r="E2" s="277"/>
-      <c r="F2" s="277"/>
-      <c r="G2" s="277"/>
-      <c r="H2" s="278"/>
+      <c r="C2" s="303"/>
+      <c r="D2" s="293" t="s">
+        <v>277</v>
+      </c>
+      <c r="E2" s="294"/>
+      <c r="F2" s="294"/>
+      <c r="G2" s="294"/>
+      <c r="H2" s="295"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="290" t="s">
+      <c r="B3" s="280" t="s">
         <v>115</v>
       </c>
-      <c r="C3" s="291"/>
-      <c r="D3" s="294" t="s">
-        <v>281</v>
-      </c>
-      <c r="E3" s="295"/>
-      <c r="F3" s="295"/>
-      <c r="G3" s="295"/>
-      <c r="H3" s="296"/>
-    </row>
-    <row r="4" spans="2:14" ht="13.5" thickBot="1">
-      <c r="B4" s="292" t="s">
+      <c r="C3" s="281"/>
+      <c r="D3" s="304" t="s">
+        <v>278</v>
+      </c>
+      <c r="E3" s="305"/>
+      <c r="F3" s="305"/>
+      <c r="G3" s="305"/>
+      <c r="H3" s="306"/>
+    </row>
+    <row r="4" spans="2:14" ht="14.25" thickBot="1">
+      <c r="B4" s="291" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="293"/>
-      <c r="D4" s="279" t="str">
+      <c r="C4" s="292"/>
+      <c r="D4" s="296" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_C_AVSWAR-CSTD-A0-03-A-C0.c</v>
       </c>
-      <c r="E4" s="280"/>
-      <c r="F4" s="280"/>
-      <c r="G4" s="280"/>
-      <c r="H4" s="281"/>
-    </row>
-    <row r="5" spans="2:14" ht="13.5" thickBot="1">
+      <c r="E4" s="297"/>
+      <c r="F4" s="297"/>
+      <c r="G4" s="297"/>
+      <c r="H4" s="298"/>
+    </row>
+    <row r="5" spans="2:14" ht="14.25" thickBot="1">
       <c r="D5" t="str">
         <f ca="1">IF(LEN(表紙!D3&amp;".c") = LENB(表紙!D3&amp;".c"),"※モジュール名 全角チェックOK","※モジュール名 全角チェックNG：ファイル名に全角文字が使用されています！")</f>
         <v>※モジュール名 全角チェックOK</v>
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="288" t="s">
+      <c r="B6" s="302" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="289"/>
-      <c r="D6" s="282" t="str">
+      <c r="C6" s="303"/>
+      <c r="D6" s="299" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>C_AVSWAR</v>
       </c>
-      <c r="E6" s="283"/>
-      <c r="F6" s="283"/>
-      <c r="G6" s="283"/>
-      <c r="H6" s="284"/>
+      <c r="E6" s="300"/>
+      <c r="F6" s="300"/>
+      <c r="G6" s="300"/>
+      <c r="H6" s="301"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="290" t="s">
+      <c r="B7" s="280" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="291"/>
-      <c r="D7" s="285">
+      <c r="C7" s="281"/>
+      <c r="D7" s="282">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="286"/>
-      <c r="F7" s="286"/>
-      <c r="G7" s="286"/>
-      <c r="H7" s="287"/>
+      <c r="E7" s="283"/>
+      <c r="F7" s="283"/>
+      <c r="G7" s="283"/>
+      <c r="H7" s="284"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="290" t="s">
+      <c r="B8" s="280" t="s">
         <v>94</v>
       </c>
-      <c r="C8" s="291"/>
-      <c r="D8" s="285" t="str">
+      <c r="C8" s="281"/>
+      <c r="D8" s="282" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_C_AVSWAR_MTRX</v>
       </c>
-      <c r="E8" s="286"/>
-      <c r="F8" s="286"/>
-      <c r="G8" s="286"/>
-      <c r="H8" s="287"/>
+      <c r="E8" s="283"/>
+      <c r="F8" s="283"/>
+      <c r="G8" s="283"/>
+      <c r="H8" s="284"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="290" t="s">
+      <c r="B9" s="280" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="291"/>
-      <c r="D9" s="297" t="s">
+      <c r="C9" s="281"/>
+      <c r="D9" s="285" t="s">
         <v>206</v>
       </c>
-      <c r="E9" s="298"/>
-      <c r="F9" s="298"/>
-      <c r="G9" s="298"/>
-      <c r="H9" s="299"/>
-    </row>
-    <row r="10" spans="2:14" ht="13.5" thickBot="1">
-      <c r="B10" s="292" t="s">
+      <c r="E9" s="286"/>
+      <c r="F9" s="286"/>
+      <c r="G9" s="286"/>
+      <c r="H9" s="287"/>
+    </row>
+    <row r="10" spans="2:14" ht="14.25" thickBot="1">
+      <c r="B10" s="291" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="293"/>
-      <c r="D10" s="300" t="s">
+      <c r="C10" s="292"/>
+      <c r="D10" s="288" t="s">
         <v>200</v>
       </c>
-      <c r="E10" s="301"/>
-      <c r="F10" s="301"/>
-      <c r="G10" s="301"/>
-      <c r="H10" s="302"/>
-    </row>
-    <row r="11" spans="2:14" ht="13.5" thickBot="1"/>
-    <row r="12" spans="2:14" ht="13.5" thickBot="1">
+      <c r="E10" s="289"/>
+      <c r="F10" s="289"/>
+      <c r="G10" s="289"/>
+      <c r="H10" s="290"/>
+    </row>
+    <row r="11" spans="2:14" ht="14.25" thickBot="1"/>
+    <row r="12" spans="2:14" ht="14.25" thickBot="1">
       <c r="B12" s="134" t="s">
         <v>33</v>
       </c>
@@ -13056,7 +13342,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="13.5" thickTop="1">
+    <row r="13" spans="2:14" ht="14.25" thickTop="1">
       <c r="B13" s="102">
         <v>1</v>
       </c>
@@ -13067,7 +13353,7 @@
         <v>47</v>
       </c>
       <c r="E13" s="195" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F13" s="47" t="str">
         <f t="shared" ref="F13:F37" ca="1" si="0">IF($D13&lt;&gt;"","u4_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"Srcchk","")</f>
@@ -13909,7 +14195,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="13.5" thickBot="1">
+    <row r="37" spans="2:14" ht="14.25" thickBot="1">
       <c r="B37" s="93">
         <v>25</v>
       </c>
@@ -13950,12 +14236,6 @@
     <protectedRange sqref="D2:H3 D9:H10 C13:E37" name="編集許可"/>
   </protectedRanges>
   <mergeCells count="16">
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B8:C8"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="D4:H4"/>
     <mergeCell ref="D6:H6"/>
@@ -13966,6 +14246,12 @@
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D3:H3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B8:C8"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C13:C37">
@@ -14008,21 +14294,21 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B2:R59"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="36.453125" customWidth="1"/>
-    <col min="6" max="6" width="71.08984375" customWidth="1"/>
-    <col min="7" max="7" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="3.90625" customWidth="1"/>
-    <col min="16" max="16" width="9.90625" customWidth="1"/>
-    <col min="17" max="17" width="44.6328125" customWidth="1"/>
-    <col min="18" max="18" width="73.6328125" customWidth="1"/>
+    <col min="5" max="5" width="36.5" customWidth="1"/>
+    <col min="6" max="6" width="71.125" customWidth="1"/>
+    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="15" width="3.875" customWidth="1"/>
+    <col min="16" max="16" width="9.875" customWidth="1"/>
+    <col min="17" max="17" width="44.625" customWidth="1"/>
+    <col min="18" max="18" width="73.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="13.5" thickBot="1">
+    <row r="2" spans="2:18" ht="14.25" thickBot="1">
       <c r="B2" t="s">
         <v>192</v>
       </c>
@@ -14030,7 +14316,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="13.5" thickBot="1">
+    <row r="3" spans="2:18" ht="14.25" thickBot="1">
       <c r="B3" s="134" t="s">
         <v>33</v>
       </c>
@@ -14068,7 +14354,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="4" spans="2:18" ht="14.25" hidden="1" thickTop="1">
       <c r="B4" s="166">
         <v>0</v>
       </c>
@@ -14096,26 +14382,20 @@
       </c>
       <c r="R4" s="133"/>
     </row>
-    <row r="5" spans="2:18" ht="117.5" thickTop="1">
+    <row r="5" spans="2:18" ht="14.25" thickTop="1">
       <c r="B5" s="169">
         <v>1</v>
       </c>
-      <c r="C5" s="138" t="s">
-        <v>234</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>239</v>
-      </c>
+      <c r="C5" s="138"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="63" t="str">
-        <f ca="1">IF($C5&lt;&gt;"","ALERT_" &amp; D5 &amp; "_ID_"&amp;UPPER(Matrix!$D$6) &amp; "_" &amp; $C5,"")</f>
-        <v>ALERT_OPT_ID_C_AVSWAR_AVSEXT</v>
-      </c>
-      <c r="F5" s="239" t="s">
-        <v>240</v>
-      </c>
-      <c r="G5" s="63">
-        <f ca="1">IF(E5&lt;&gt;"",LEN(E5),"")</f>
-        <v>28</v>
+        <f>IF($C5&lt;&gt;"","ALERT_" &amp; D5 &amp; "_ID_"&amp;UPPER(Matrix!$D$6) &amp; "_" &amp; $C5,"")</f>
+        <v/>
+      </c>
+      <c r="F5" s="239"/>
+      <c r="G5" s="63" t="str">
+        <f>IF(E5&lt;&gt;"",LEN(E5),"")</f>
+        <v/>
       </c>
       <c r="O5" s="169">
         <v>1</v>
@@ -14630,7 +14910,7 @@
       <c r="Q28" s="138"/>
       <c r="R28" s="113"/>
     </row>
-    <row r="29" spans="2:18" ht="13.5" thickBot="1">
+    <row r="29" spans="2:18" ht="14.25" thickBot="1">
       <c r="B29" s="170">
         <v>25</v>
       </c>
@@ -14652,7 +14932,7 @@
       <c r="Q29" s="136"/>
       <c r="R29" s="115"/>
     </row>
-    <row r="32" spans="2:18" ht="13.5" thickBot="1">
+    <row r="32" spans="2:18" ht="14.25" thickBot="1">
       <c r="B32" t="s">
         <v>193</v>
       </c>
@@ -14660,7 +14940,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="13.5" thickBot="1">
+    <row r="33" spans="2:18" ht="14.25" thickBot="1">
       <c r="B33" s="134" t="s">
         <v>33</v>
       </c>
@@ -14692,7 +14972,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="34" spans="2:18" ht="14.25" hidden="1" thickTop="1">
       <c r="B34" s="166">
         <v>0</v>
       </c>
@@ -14718,7 +14998,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="13.5" thickTop="1">
+    <row r="35" spans="2:18" ht="14.25" thickTop="1">
       <c r="B35" s="169">
         <v>1</v>
       </c>
@@ -15246,7 +15526,7 @@
       <c r="Q58" s="138"/>
       <c r="R58" s="171"/>
     </row>
-    <row r="59" spans="2:18" ht="13.5" thickBot="1">
+    <row r="59" spans="2:18" ht="14.25" thickBot="1">
       <c r="B59" s="170">
         <v>25</v>
       </c>
@@ -15298,29 +15578,29 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:U103"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="28.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.90625" customWidth="1"/>
-    <col min="5" max="5" width="12.36328125" customWidth="1"/>
-    <col min="6" max="6" width="25.7265625" customWidth="1"/>
-    <col min="7" max="7" width="12.36328125" customWidth="1"/>
-    <col min="8" max="8" width="29.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.36328125" customWidth="1"/>
-    <col min="10" max="10" width="62.453125" customWidth="1"/>
-    <col min="11" max="11" width="12.36328125" customWidth="1"/>
-    <col min="12" max="12" width="16.08984375" customWidth="1"/>
-    <col min="14" max="14" width="30.08984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="57.08984375" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="28.375" customWidth="1"/>
+    <col min="3" max="3" width="15.875" customWidth="1"/>
+    <col min="5" max="5" width="12.375" customWidth="1"/>
+    <col min="6" max="6" width="25.75" customWidth="1"/>
+    <col min="7" max="7" width="12.375" customWidth="1"/>
+    <col min="8" max="8" width="29.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.375" customWidth="1"/>
+    <col min="10" max="10" width="62.5" customWidth="1"/>
+    <col min="11" max="11" width="12.375" customWidth="1"/>
+    <col min="12" max="12" width="16.125" customWidth="1"/>
+    <col min="14" max="14" width="30.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="57.125" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="13.5" thickBot="1">
+    <row r="1" spans="2:21" ht="14.25" thickBot="1">
       <c r="C1" s="86" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="13.5" thickBot="1">
+    <row r="2" spans="2:21" ht="14.25" thickBot="1">
       <c r="B2" s="94" t="s">
         <v>57</v>
       </c>
@@ -15364,7 +15644,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="14" hidden="1" thickTop="1" thickBot="1">
+    <row r="3" spans="2:21" ht="15" hidden="1" thickTop="1" thickBot="1">
       <c r="B3" s="24"/>
       <c r="C3" s="46" t="s">
         <v>107</v>
@@ -15385,12 +15665,12 @@
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="13.5" thickTop="1">
+    <row r="4" spans="2:21" ht="14.25" thickTop="1">
       <c r="B4" s="105" t="s">
+        <v>243</v>
+      </c>
+      <c r="C4" s="104" t="s">
         <v>246</v>
-      </c>
-      <c r="C4" s="104" t="s">
-        <v>249</v>
       </c>
       <c r="D4" s="116">
         <v>0</v>
@@ -15408,13 +15688,13 @@
         <v>227</v>
       </c>
       <c r="I4" s="189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J4" s="190" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K4" s="189" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="L4" s="190" t="s">
         <v>30</v>
@@ -15440,7 +15720,7 @@
         <v>233</v>
       </c>
       <c r="C5" s="104" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D5" s="116">
         <v>1</v>
@@ -15458,10 +15738,10 @@
         <v>154</v>
       </c>
       <c r="I5" s="189" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J5" s="196" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K5" s="189" t="s">
         <v>212</v>
@@ -15675,7 +15955,7 @@
       </c>
       <c r="U12" s="26"/>
     </row>
-    <row r="13" spans="2:21" ht="13.5" thickBot="1">
+    <row r="13" spans="2:21" ht="14.25" thickBot="1">
       <c r="B13" s="24"/>
       <c r="C13" s="23"/>
       <c r="D13" s="112"/>
@@ -17926,7 +18206,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="2:15" ht="13.5" thickBot="1">
+    <row r="103" spans="2:15" ht="14.25" thickBot="1">
       <c r="B103" s="48"/>
       <c r="C103" s="49"/>
       <c r="D103" s="114"/>
@@ -18000,20 +18280,20 @@
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6" style="183" customWidth="1"/>
-    <col min="2" max="2" width="16.7265625" style="183" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.75" style="183" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3" style="183" bestFit="1" customWidth="1"/>
     <col min="4" max="35" width="3" style="183" customWidth="1"/>
-    <col min="36" max="36" width="36.36328125" style="183" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.08984375" style="183" customWidth="1"/>
+    <col min="36" max="36" width="36.375" style="183" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.125" style="183" customWidth="1"/>
     <col min="38" max="42" width="9" style="183" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="20.6328125" style="183" hidden="1" customWidth="1"/>
-    <col min="44" max="45" width="41.08984375" style="183" customWidth="1"/>
+    <col min="43" max="43" width="20.625" style="183" hidden="1" customWidth="1"/>
+    <col min="44" max="45" width="41.125" style="183" customWidth="1"/>
     <col min="46" max="46" width="37" style="183" customWidth="1"/>
-    <col min="47" max="47" width="41.08984375" style="183" customWidth="1"/>
-    <col min="48" max="48" width="23.6328125" style="183" customWidth="1"/>
+    <col min="47" max="47" width="41.125" style="183" customWidth="1"/>
+    <col min="48" max="48" width="23.625" style="183" customWidth="1"/>
     <col min="49" max="49" width="29" style="183" bestFit="1" customWidth="1"/>
     <col min="50" max="16384" width="9" style="183"/>
   </cols>
@@ -18030,7 +18310,7 @@
       <c r="B2" s="121" t="s">
         <v>122</v>
       </c>
-      <c r="C2" s="307" t="s">
+      <c r="C2" s="311" t="s">
         <v>83</v>
       </c>
       <c r="D2" s="53">
@@ -18129,7 +18409,7 @@
       <c r="AI2" s="53">
         <v>0</v>
       </c>
-      <c r="AJ2" s="309" t="s">
+      <c r="AJ2" s="313" t="s">
         <v>121</v>
       </c>
     </row>
@@ -18138,7 +18418,7 @@
         <f>IF(OR(IF(COUNTIF(D6:AC69,"0")&lt;&gt;0,TRUE,FALSE),IF(COUNTIF(D6:AC69,"1")&lt;&gt;0,TRUE,FALSE)),"Search Table","Index Table")</f>
         <v>Index Table</v>
       </c>
-      <c r="C3" s="308"/>
+      <c r="C3" s="312"/>
       <c r="D3" s="123" t="s">
         <v>60</v>
       </c>
@@ -18220,25 +18500,25 @@
       <c r="AD3" s="124" t="s">
         <v>61</v>
       </c>
-      <c r="AE3" s="311" t="s">
-        <v>242</v>
-      </c>
-      <c r="AF3" s="313"/>
-      <c r="AG3" s="311" t="s">
-        <v>241</v>
-      </c>
-      <c r="AH3" s="312"/>
-      <c r="AI3" s="313"/>
-      <c r="AJ3" s="310"/>
+      <c r="AE3" s="315" t="s">
+        <v>239</v>
+      </c>
+      <c r="AF3" s="317"/>
+      <c r="AG3" s="315" t="s">
+        <v>238</v>
+      </c>
+      <c r="AH3" s="316"/>
+      <c r="AI3" s="317"/>
+      <c r="AJ3" s="314"/>
       <c r="AR3" s="87" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="13.5" thickBot="1">
-      <c r="A4" s="303" t="s">
+    <row r="4" spans="1:49" ht="14.25" thickBot="1">
+      <c r="A4" s="307" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="304"/>
+      <c r="B4" s="308"/>
       <c r="C4" s="184"/>
       <c r="D4" s="184"/>
       <c r="E4" s="184"/>
@@ -18282,9 +18562,9 @@
       <c r="AV4" s="76"/>
       <c r="AW4" s="77"/>
     </row>
-    <row r="5" spans="1:49" ht="13.5" thickBot="1">
-      <c r="A5" s="305"/>
-      <c r="B5" s="306"/>
+    <row r="5" spans="1:49" ht="14.25" thickBot="1">
+      <c r="A5" s="309"/>
+      <c r="B5" s="310"/>
       <c r="C5" s="185"/>
       <c r="D5" s="185"/>
       <c r="E5" s="185"/>
@@ -18447,7 +18727,7 @@
         <v>0</v>
       </c>
       <c r="AJ6" s="103" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AL6" s="183" t="str">
         <f t="shared" ref="AL6:AL69" si="0">IF($AJ6="UNKNOWN","    (U1)ALERT_REQ_UNKNOWN","    (U1)"&amp;"ALERT_REQ_"&amp;$AW$17&amp;"_"&amp;IF($AW$6&lt;&gt;$AW$17,$AW$6&amp;"_","")&amp;AJ6)</f>
@@ -18579,7 +18859,7 @@
         <v>1</v>
       </c>
       <c r="AJ7" s="103" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AL7" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18712,7 +18992,7 @@
         <v>0</v>
       </c>
       <c r="AJ8" s="103" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AL8" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18845,7 +19125,7 @@
         <v>1</v>
       </c>
       <c r="AJ9" s="103" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AL9" s="183" t="str">
         <f t="shared" si="0"/>
@@ -18975,7 +19255,7 @@
         <v>0</v>
       </c>
       <c r="AJ10" s="103" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AL10" s="183" t="str">
         <f t="shared" si="0"/>
@@ -19108,7 +19388,7 @@
         <v>1</v>
       </c>
       <c r="AJ11" s="103" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AL11" s="183" t="str">
         <f t="shared" si="0"/>
@@ -19241,7 +19521,7 @@
         <v>0</v>
       </c>
       <c r="AJ12" s="103" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AL12" s="183" t="str">
         <f t="shared" si="0"/>
@@ -19371,7 +19651,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" s="103" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AL13" s="183" t="str">
         <f t="shared" si="0"/>
@@ -19504,7 +19784,7 @@
         <v>0</v>
       </c>
       <c r="AJ14" s="103" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AL14" s="183" t="str">
         <f t="shared" si="0"/>
@@ -19637,7 +19917,7 @@
         <v>1</v>
       </c>
       <c r="AJ15" s="103" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AL15" s="183" t="str">
         <f t="shared" si="0"/>
@@ -19770,7 +20050,7 @@
         <v>0</v>
       </c>
       <c r="AJ16" s="103" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AL16" s="183" t="str">
         <f t="shared" si="0"/>
@@ -19799,7 +20079,7 @@
         <v>ALERT_VOM_IGN_ON</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="13.5" thickBot="1">
+    <row r="17" spans="2:49" ht="14.25" thickBot="1">
       <c r="B17" s="130"/>
       <c r="C17" s="42">
         <f t="shared" si="2"/>
@@ -19902,7 +20182,7 @@
         <v>1</v>
       </c>
       <c r="AJ17" s="103" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AL17" s="183" t="str">
         <f t="shared" si="0"/>
@@ -20034,7 +20314,7 @@
         <v>0</v>
       </c>
       <c r="AJ18" s="103" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AL18" s="183" t="str">
         <f t="shared" si="0"/>
@@ -20156,7 +20436,7 @@
         <v>1</v>
       </c>
       <c r="AJ19" s="103" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AL19" s="183" t="str">
         <f t="shared" si="0"/>
@@ -20278,7 +20558,7 @@
         <v>0</v>
       </c>
       <c r="AJ20" s="103" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AL20" s="183" t="str">
         <f t="shared" si="0"/>
@@ -20400,7 +20680,7 @@
         <v>1</v>
       </c>
       <c r="AJ21" s="103" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AL21" s="183" t="str">
         <f t="shared" si="0"/>
@@ -20522,7 +20802,7 @@
         <v>0</v>
       </c>
       <c r="AJ22" s="103" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AL22" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20644,7 +20924,7 @@
         <v>1</v>
       </c>
       <c r="AJ23" s="103" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AL23" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20766,7 +21046,7 @@
         <v>0</v>
       </c>
       <c r="AJ24" s="103" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AL24" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20888,7 +21168,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" s="103" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AL25" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21010,7 +21290,7 @@
         <v>0</v>
       </c>
       <c r="AJ26" s="103" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AL26" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21132,7 +21412,7 @@
         <v>1</v>
       </c>
       <c r="AJ27" s="103" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AL27" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21254,7 +21534,7 @@
         <v>0</v>
       </c>
       <c r="AJ28" s="103" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AL28" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21376,7 +21656,7 @@
         <v>1</v>
       </c>
       <c r="AJ29" s="103" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AL29" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21498,7 +21778,7 @@
         <v>0</v>
       </c>
       <c r="AJ30" s="103" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AL30" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21620,7 +21900,7 @@
         <v>1</v>
       </c>
       <c r="AJ31" s="103" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AL31" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21742,7 +22022,7 @@
         <v>0</v>
       </c>
       <c r="AJ32" s="103" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AL32" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21864,7 +22144,7 @@
         <v>1</v>
       </c>
       <c r="AJ33" s="103" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AL33" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21986,7 +22266,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="103" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AL34" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22108,7 +22388,7 @@
         <v>1</v>
       </c>
       <c r="AJ35" s="103" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AL35" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22230,7 +22510,7 @@
         <v>0</v>
       </c>
       <c r="AJ36" s="103" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AL36" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22352,7 +22632,7 @@
         <v>1</v>
       </c>
       <c r="AJ37" s="103" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AL37" s="183" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -26211,7 +26491,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="13.5" thickBot="1">
+    <row r="70" spans="1:46" ht="14.25" thickBot="1">
       <c r="A70" s="51" t="s">
         <v>63</v>
       </c>
@@ -46839,22 +47119,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:CY117"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="71.90625" customWidth="1"/>
-    <col min="3" max="10" width="3.36328125" customWidth="1"/>
-    <col min="11" max="11" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.875" customWidth="1"/>
+    <col min="3" max="10" width="3.375" customWidth="1"/>
+    <col min="11" max="11" width="19.75" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.25" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="20" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.08984375" customWidth="1"/>
-    <col min="15" max="15" width="29.26953125" customWidth="1"/>
+    <col min="14" max="14" width="17.125" customWidth="1"/>
+    <col min="15" max="15" width="29.25" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="10.90625" customWidth="1"/>
+    <col min="17" max="17" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="14.5" thickBot="1">
+    <row r="2" spans="2:17" ht="15" thickBot="1">
       <c r="B2" s="243" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C2" s="183"/>
       <c r="D2" s="183"/>
@@ -46872,20 +47152,20 @@
       <c r="P2" s="183"/>
       <c r="Q2" s="183"/>
     </row>
-    <row r="3" spans="2:17" ht="14.5" thickBot="1">
+    <row r="3" spans="2:17" ht="15" thickBot="1">
       <c r="B3" s="91" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="314" t="s">
+      <c r="C3" s="318" t="s">
         <v>201</v>
       </c>
-      <c r="D3" s="315"/>
-      <c r="E3" s="315"/>
-      <c r="F3" s="315"/>
-      <c r="G3" s="315"/>
-      <c r="H3" s="315"/>
-      <c r="I3" s="315"/>
-      <c r="J3" s="316"/>
+      <c r="D3" s="319"/>
+      <c r="E3" s="319"/>
+      <c r="F3" s="319"/>
+      <c r="G3" s="319"/>
+      <c r="H3" s="319"/>
+      <c r="I3" s="319"/>
+      <c r="J3" s="320"/>
       <c r="K3" s="162"/>
       <c r="L3" s="162"/>
       <c r="M3" s="165"/>
@@ -46922,22 +47202,22 @@
       <c r="B5" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="317" t="s">
+      <c r="C5" s="321" t="s">
         <v>170</v>
       </c>
-      <c r="D5" s="318"/>
-      <c r="E5" s="318"/>
-      <c r="F5" s="318"/>
-      <c r="G5" s="318"/>
-      <c r="H5" s="318"/>
-      <c r="I5" s="318"/>
-      <c r="J5" s="319"/>
+      <c r="D5" s="322"/>
+      <c r="E5" s="322"/>
+      <c r="F5" s="322"/>
+      <c r="G5" s="322"/>
+      <c r="H5" s="322"/>
+      <c r="I5" s="322"/>
+      <c r="J5" s="323"/>
       <c r="K5" s="218" t="s">
         <v>228</v>
       </c>
       <c r="L5" s="219"/>
       <c r="M5" s="26" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="N5" s="71" t="s">
         <v>22</v>
@@ -46952,7 +47232,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="39">
+    <row r="6" spans="2:17" ht="40.5">
       <c r="B6" s="66" t="s">
         <v>32</v>
       </c>
@@ -46993,38 +47273,38 @@
       <c r="O6" s="35"/>
       <c r="P6" s="72"/>
       <c r="Q6" s="85" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="7" spans="2:17" ht="26">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" ht="27">
       <c r="B7" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="320" t="s">
+      <c r="C7" s="324" t="s">
         <v>150</v>
       </c>
-      <c r="D7" s="318"/>
-      <c r="E7" s="318"/>
-      <c r="F7" s="318"/>
-      <c r="G7" s="318"/>
-      <c r="H7" s="318"/>
-      <c r="I7" s="318"/>
-      <c r="J7" s="319"/>
+      <c r="D7" s="322"/>
+      <c r="E7" s="322"/>
+      <c r="F7" s="322"/>
+      <c r="G7" s="322"/>
+      <c r="H7" s="322"/>
+      <c r="I7" s="322"/>
+      <c r="J7" s="323"/>
       <c r="K7" s="222" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L7" s="222" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="M7" s="27"/>
       <c r="N7" s="72"/>
       <c r="O7" s="35"/>
       <c r="P7" s="72"/>
       <c r="Q7" s="69" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="8" spans="2:17" ht="131">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" ht="136.5">
       <c r="B8" s="66" t="s">
         <v>27</v>
       </c>
@@ -47053,10 +47333,10 @@
         <v>160</v>
       </c>
       <c r="K8" s="222" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L8" s="222" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="M8" s="26" t="s">
         <v>28</v>
@@ -47065,7 +47345,7 @@
       <c r="O8" s="35"/>
       <c r="P8" s="72"/>
       <c r="Q8" s="69" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="9" spans="2:17" ht="154.5" customHeight="1" thickBot="1">
@@ -47097,26 +47377,26 @@
         <v>162</v>
       </c>
       <c r="K9" s="223" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="L9" s="224" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="M9" s="28" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="N9" s="70"/>
       <c r="O9" s="241" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="P9" s="70"/>
       <c r="Q9" s="240" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="10" spans="2:17" ht="13.5" thickTop="1">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" ht="14.25" thickTop="1">
       <c r="B10" s="235" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C10" s="159" t="s">
         <v>161</v>
@@ -47146,7 +47426,7 @@
         <v>204</v>
       </c>
       <c r="L10" s="226" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="M10" s="227" t="s">
         <v>107</v>
@@ -47162,7 +47442,7 @@
     </row>
     <row r="11" spans="2:17">
       <c r="B11" s="236" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C11" s="159" t="s">
         <v>161</v>
@@ -47189,26 +47469,26 @@
         <v>161</v>
       </c>
       <c r="K11" s="217" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="L11" s="228" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="M11" s="31" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="N11" s="233"/>
       <c r="O11" s="232" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="P11" s="233"/>
       <c r="Q11" s="228" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="2:17">
       <c r="B12" s="236" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C12" s="159" t="s">
         <v>161</v>
@@ -47235,17 +47515,17 @@
         <v>161</v>
       </c>
       <c r="K12" s="217" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="L12" s="228" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M12" s="30" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="N12" s="36"/>
       <c r="O12" s="232" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="P12" s="36"/>
       <c r="Q12" s="228" t="s">
@@ -47254,7 +47534,7 @@
     </row>
     <row r="13" spans="2:17">
       <c r="B13" s="236" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C13" s="160" t="s">
         <v>161</v>
@@ -47281,10 +47561,10 @@
         <v>161</v>
       </c>
       <c r="K13" s="217" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="L13" s="228" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="M13" s="30" t="s">
         <v>31</v>
@@ -47300,7 +47580,7 @@
     </row>
     <row r="14" spans="2:17" s="183" customFormat="1">
       <c r="B14" s="236" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C14" s="160" t="s">
         <v>161</v>
@@ -47327,10 +47607,10 @@
         <v>161</v>
       </c>
       <c r="K14" s="238" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="L14" s="228" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="M14" s="30" t="s">
         <v>31</v>
@@ -47346,7 +47626,7 @@
     </row>
     <row r="15" spans="2:17" s="183" customFormat="1">
       <c r="B15" s="236" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C15" s="160" t="s">
         <v>161</v>
@@ -47376,23 +47656,23 @@
         <v>207</v>
       </c>
       <c r="L15" s="228" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M15" s="31" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="N15" s="36"/>
       <c r="O15" s="232" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="P15" s="36"/>
       <c r="Q15" s="228" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="2:17" s="183" customFormat="1">
       <c r="B16" s="236" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C16" s="160" t="s">
         <v>161</v>
@@ -47422,21 +47702,21 @@
         <v>208</v>
       </c>
       <c r="L16" s="228" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M16" s="31" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="N16" s="36"/>
       <c r="O16" s="232" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="P16" s="36"/>
       <c r="Q16" s="228" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="17" spans="2:61" ht="13.5" thickBot="1">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="17" spans="2:61" ht="14.25" thickBot="1">
       <c r="B17" s="21" t="s">
         <v>232</v>
       </c>
@@ -48560,16 +48840,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:D27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="183"/>
-    <col min="2" max="2" width="4.90625" style="183" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.26953125" style="183" customWidth="1"/>
+    <col min="2" max="2" width="4.875" style="183" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.25" style="183" customWidth="1"/>
     <col min="4" max="4" width="86" style="183" customWidth="1"/>
     <col min="5" max="16384" width="9" style="183"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="13.5" thickBot="1">
+    <row r="2" spans="2:4" ht="14.25" thickBot="1">
       <c r="B2" s="79" t="s">
         <v>84</v>
       </c>
@@ -48579,7 +48859,7 @@
       </c>
       <c r="D2" s="80"/>
     </row>
-    <row r="3" spans="2:4" ht="13.5" thickBot="1">
+    <row r="3" spans="2:4" ht="14.25" thickBot="1">
       <c r="B3" s="73" t="s">
         <v>84</v>
       </c>
@@ -48590,7 +48870,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="13.5" thickTop="1">
+    <row r="4" spans="2:4" ht="14.25" thickTop="1">
       <c r="B4" s="12">
         <v>0</v>
       </c>
@@ -48601,7 +48881,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="39">
+    <row r="5" spans="2:4" ht="40.5">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -48612,7 +48892,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="26">
+    <row r="6" spans="2:4" ht="27">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -48623,7 +48903,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="52">
+    <row r="7" spans="2:4" ht="54">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -48634,7 +48914,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="78">
+    <row r="8" spans="2:4" ht="81">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -48656,7 +48936,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="26">
+    <row r="10" spans="2:4" ht="27">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -48667,7 +48947,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="26">
+    <row r="11" spans="2:4" ht="27">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -48678,7 +48958,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="26">
+    <row r="12" spans="2:4" ht="27">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -48689,7 +48969,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="26">
+    <row r="13" spans="2:4" ht="27">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -48700,7 +48980,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="26">
+    <row r="14" spans="2:4" ht="27">
       <c r="B14" s="2">
         <v>10</v>
       </c>
@@ -48711,7 +48991,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="130">
+    <row r="15" spans="2:4" ht="135">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -48733,7 +49013,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="26">
+    <row r="17" spans="2:4" ht="27">
       <c r="B17" s="2">
         <v>13</v>
       </c>
@@ -48744,7 +49024,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="91">
+    <row r="18" spans="2:4" ht="67.5">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -48755,7 +49035,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="39">
+    <row r="19" spans="2:4" ht="40.5">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -48788,7 +49068,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="26">
+    <row r="22" spans="2:4" ht="27">
       <c r="B22" s="2">
         <v>18</v>
       </c>
@@ -48799,7 +49079,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="26">
+    <row r="23" spans="2:4" ht="27">
       <c r="B23" s="2">
         <v>19</v>
       </c>
@@ -48810,7 +49090,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="24" spans="2:4" ht="91">
+    <row r="24" spans="2:4" ht="94.5">
       <c r="B24" s="2">
         <v>20</v>
       </c>
@@ -48831,7 +49111,7 @@
       <c r="C26" s="83"/>
       <c r="D26" s="69"/>
     </row>
-    <row r="27" spans="2:4" ht="13.5" thickBot="1">
+    <row r="27" spans="2:4" ht="14.25" thickBot="1">
       <c r="B27" s="3"/>
       <c r="C27" s="84"/>
       <c r="D27" s="5"/>
